--- a/input/mapping/001. OCB_GOLD_TCKH_V_BCN_THUNO_QUANG.xlsx
+++ b/input/mapping/001. OCB_GOLD_TCKH_V_BCN_THUNO_QUANG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ZoneC_BOC\V_BCN_THUNO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{B3BC50D8-8E3D-4A21-B485-C15EB2612AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C27A61F4-1C4A-49F1-9BDD-842991744182}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{B3BC50D8-8E3D-4A21-B485-C15EB2612AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDBAB7F0-ABF3-4843-99F5-31D819F952D1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="150">
   <si>
     <t>V_BCN_THUNO  —  DATA LINEAGE</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>Layer 3</t>
+  </si>
+  <si>
+    <t>Layer 4</t>
   </si>
   <si>
     <t>DATAMART-THUNO</t>
@@ -98,6 +101,9 @@
   </si>
   <si>
     <t>danh_branches</t>
+  </si>
+  <si>
+    <t>customer_custgroup_map</t>
   </si>
   <si>
     <t>T24_CUSTOMER</t>
@@ -281,6 +287,786 @@
       AND bcn.LD_NO     = bundle.LD_NO;</t>
   </si>
   <si>
+    <t>code mới</t>
+  </si>
+  <si>
+    <t>tb_bcn085_thuno_dtl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
+USE SCHEMA tckh;
+DELETE FROM tb_bcn085_thuno_dtl
+WHERE  DATA_DATE = CAST(:DATADT AS STRING);
+INSERT INTO tb_bcn085_thuno_dtl
+    (ROWNUM, THOAILAIDUTHU, BRANCH_PARENT_CODE, DATA_DATE, TOTAL_AMOUNT_EQ, THU_PS, FULL_NAME,
+     BRANCH_CODE, PDDAYS_PR_D_1, PDDAYS_IN_D_1, INTERATE_RATE, CURRENCY, CIF, LN_CLS_D_1,
+     THU_PE, LD_NO, TK_THUNO, THU_PHI, BRANCH_PARENT_NAME, NGAY_GIAI_NGAN, THU_IN, BRANCH_NAME,
+     LOAN_CLASSIFICATION, CUSTGROUP_DESCRIPTION, TOTAL_AMOUNT, THU_GOC)
+WITH
+prev_wd AS (
+    SELECT CAST(LAST_WK_ID AS INT) AS wd_int
+    FROM   IDENTIFIER(:cleaned || '.business_vault.calendar')
+    WHERE  MSR_PRD_ID = CAST(:DATADT AS INT)
+),
+loans_sts_del AS (
+    SELECT loans_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sts_hub_loans')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY loans_hashkey
+    HAVING max_by(cdc_status, source_event_date) = 'D'
+),
+loans_hub AS (
+    SELECT loans_hashkey, business_key
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.hub_loans')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY loans_hashkey, business_key
+),
+loans_active AS (
+    SELECT h.loans_hashkey, h.business_key
+    FROM      loans_hub h
+    LEFT JOIN loans_sts_del x ON x.loans_hashkey = h.loans_hashkey
+    WHERE  x.loans_hashkey IS NULL
+),
+branch_sts_del AS (
+    SELECT branch_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sts_hub_branch')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY branch_hashkey
+    HAVING max_by(cdc_status, source_event_date) = 'D'
+),
+branch_hub AS (
+    SELECT branch_hashkey, business_key
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.hub_branch')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY branch_hashkey, business_key
+),
+branch_active AS (
+    SELECT h.branch_hashkey, h.business_key
+    FROM      branch_hub h
+    LEFT JOIN branch_sts_del x ON x.branch_hashkey = h.branch_hashkey
+    WHERE  x.branch_hashkey IS NULL
+),
+customer_sts_del AS (
+    SELECT customer_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sts_hub_customer')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY customer_hashkey
+    HAVING max_by(cdc_status, source_event_date) = 'D'
+),
+customer_hub AS (
+    SELECT customer_hashkey, business_key
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.hub_customer')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY customer_hashkey, business_key
+),
+customer_active AS (
+    SELECT h.customer_hashkey, h.business_key
+    FROM      customer_hub h
+    LEFT JOIN customer_sts_del x ON x.customer_hashkey = h.customer_hashkey
+    WHERE  x.customer_hashkey IS NULL
+),
+pd_sts_del AS (
+    SELECT s.loans_payment_due_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sts_hub_loans_payment_due') s, prev_wd w
+    WHERE  s.source_event_date &lt;= TO_DATE(CAST(w.wd_int AS STRING),'yyyyMMdd')
+    GROUP BY s.loans_payment_due_hashkey
+    HAVING max_by(s.cdc_status, s.source_event_date) = 'D'
+),
+pd_hub AS (
+    SELECT h.loans_payment_due_hashkey, h.business_key
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.hub_loans_payment_due') h, prev_wd w
+    WHERE  h.source_event_date &lt;= TO_DATE(CAST(w.wd_int AS STRING),'yyyyMMdd')
+    GROUP BY h.loans_payment_due_hashkey, h.business_key
+),
+pd_active AS (
+    SELECT h.loans_payment_due_hashkey, h.business_key
+    FROM      pd_hub h
+    LEFT JOIN pd_sts_del x ON x.loans_payment_due_hashkey = h.loans_payment_due_hashkey
+    WHERE  x.loans_payment_due_hashkey IS NULL
+),
+stmt_hub AS (
+    SELECT stmt_entry_hashkey, business_key
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.hub_stmt_entry')
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+),
+sat_stmt_info AS (
+    SELECT stmt_entry_hashkey,
+           max_by(t_trans_reference, source_event_date) AS t_trans_reference,
+           max_by(t_account_number,  source_event_date) AS t_account_number,
+           max_by(t_amount_lcy,      source_event_date) AS t_amount_lcy
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_information')
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY stmt_entry_hashkey
+),
+sat_stmt_cls AS (
+    SELECT stmt_entry_hashkey,
+           max_by(t_transaction_code, source_event_date) AS t_transaction_code
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_classification')
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY stmt_entry_hashkey
+),
+sat_stmt_audit AS (
+    SELECT stmt_entry_hashkey,
+           max_by(t_record_status, source_event_date) AS t_record_status
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_stmt_entry_audit')
+    WHERE  source_event_date = TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY stmt_entry_hashkey
+),
+sat_ld_terms AS (
+    SELECT loans_hashkey,
+           max_by(t_value_date, source_event_date) AS t_value_date
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_loans_terms')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY loans_hashkey
+),
+sat_cust_info AS (
+    SELECT customer_hashkey,
+           max_by(name_1, source_event_date) AS name_1,
+           max_by(name_2, source_event_date) AS name_2
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_customer_information')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY customer_hashkey
+),
+sat_cust_cls AS (
+    SELECT customer_hashkey,
+           max_by(cust_group, source_event_date) AS cust_group,
+           max_by(sector,     source_event_date) AS sector
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_customer_classification')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY customer_hashkey
+),
+ref_sector AS (
+    SELECT ref_code,
+           max_by(t_sector_group, source_event_date) AS t_sector_group
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.ref_t24_sector')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY ref_code
+),
+sat_pd_over AS (
+    SELECT so.loans_payment_due_hashkey,
+           max_by(so.t_pay_type,     so.source_event_date) AS t_pay_type,
+           max_by(so.t_pay_amt_outs, so.source_event_date) AS t_pay_amt_outs
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_loans_payment_due_overdue') so, prev_wd w
+    WHERE  so.source_event_date &lt;= TO_DATE(CAST(w.wd_int AS STRING),'yyyyMMdd')
+    GROUP BY so.loans_payment_due_hashkey
+),
+sat_pd_info AS (
+    SELECT si.loans_payment_due_hashkey,
+           max_by(si.t_payment_dte_due, si.source_event_date) AS t_payment_dte_due
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_loans_payment_due_information') si, prev_wd w
+    WHERE  si.source_event_date &lt;= TO_DATE(CAST(w.wd_int AS STRING),'yyyyMMdd')
+    GROUP BY si.loans_payment_due_hashkey
+),
+lnk_loans_customer AS (
+    SELECT loans_hashkey,
+           max_by(customer_hashkey, source_event_date) AS customer_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_loans_customer')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY loans_hashkey
+),
+lnk_loans_branch AS (
+    SELECT loans_hashkey,
+           max_by(branch_hashkey, source_event_date) AS branch_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_loans_branch')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY loans_hashkey
+),
+br_raw AS (
+    SELECT MACN, MACN_QL, TENCN, TENCN_QL
+    FROM   danh_branches
+),
+cust_name AS (
+    SELECT hc.business_key AS cif,
+           TRIM(CONCAT(REPLACE(COALESCE(si.name_1,''),'::',' '),
+                       REPLACE(COALESCE(si.name_2,''),'::',''))) AS full_name
+    FROM      customer_active hc
+    LEFT JOIN sat_cust_info   si ON si.customer_hashkey = hc.customer_hashkey
+),
+cust_class AS (
+    SELECT hc.business_key AS cif,
+           CASE WHEN sc.cust_group IS NULL
+                THEN (CASE WHEN CAST(rs.t_sector_group AS INT) IN (1,4,5) THEN 1 ELSE 2 END)
+                ELSE CAST(sc.cust_group AS INT) END AS custgroup
+    FROM      customer_active hc
+    LEFT JOIN sat_cust_cls    sc ON sc.customer_hashkey = hc.customer_hashkey
+    LEFT JOIN ref_sector      rs ON CAST(rs.ref_code AS STRING) = CAST(sc.sector AS STRING)
+),
+cust_grp AS (
+    SELECT k.cif, m.custgroup_description_vn AS custgroup_description
+    FROM      cust_class k
+    LEFT JOIN customer_custgroup_map m
+           ON CAST(m.custgroup AS STRING) = CAST(k.custgroup AS STRING)
+),
+stmt_all AS (
+    SELECT h.business_key AS id, i.t_trans_reference, i.t_account_number, i.t_amount_lcy,
+           cl.t_transaction_code, a.t_record_status
+    FROM      stmt_hub       h
+    LEFT JOIN sat_stmt_info  i  ON i.stmt_entry_hashkey  = h.stmt_entry_hashkey
+    LEFT JOIN sat_stmt_cls   cl ON cl.stmt_entry_hashkey = h.stmt_entry_hashkey
+    LEFT JOIN sat_stmt_audit a  ON a.stmt_entry_hashkey  = h.stmt_entry_hashkey
+),
+reve AS (
+    SELECT DISTINCT t_trans_reference FROM stmt_all WHERE NVL(t_record_status,'X') = 'REVE'
+),
+thu AS (
+    SELECT
+        CASE WHEN SUBSTR(a.t_trans_reference,1,2) = 'LD' THEN SUBSTR(a.t_trans_reference,1,12)
+             ELSE SUBSTR(a.t_trans_reference,3,12) END                                     AS ld_no,
+        a.t_account_number                                                                 AS tk_thuno,
+        CASE WHEN CAST(a.t_transaction_code AS INT) = 450            THEN ABS(NVL(a.t_amount_lcy,0)) ELSE 0 END AS thoailaiduthu,
+        CASE WHEN CAST(a.t_transaction_code AS INT) IN (420,423,750) THEN ABS(NVL(a.t_amount_lcy,0)) ELSE 0 END AS thu_goc,
+        CASE WHEN CAST(a.t_transaction_code AS INT) IN (424,434,751) THEN ABS(NVL(a.t_amount_lcy,0)) ELSE 0 END AS thu_in,
+        CASE WHEN CAST(a.t_transaction_code AS INT) = 752            THEN ABS(NVL(a.t_amount_lcy,0)) ELSE 0 END AS thu_pe,
+        CASE WHEN CAST(a.t_transaction_code AS INT) = 753            THEN ABS(NVL(a.t_amount_lcy,0)) ELSE 0 END AS thu_ps,
+        CASE WHEN CAST(a.t_transaction_code AS INT) IN (429,430)     THEN ABS(NVL(a.t_amount_lcy,0)) ELSE 0 END AS thu_phi
+    FROM      stmt_all a
+    LEFT JOIN reve     r ON r.t_trans_reference = a.t_trans_reference
+    WHERE  SUBSTR(a.id,1,1) &lt;&gt; 'F'
+      AND  a.t_amount_lcy &lt; 0
+      AND  SUBSTR(a.t_trans_reference,1,2) IN ('LD','PD')
+      AND  CAST(a.t_transaction_code AS INT) IN (450,420,423,750,424,434,751,752,753,429,430)
+      AND  r.t_trans_reference IS NULL
+),
+-- lsl_snap: đọc loan_summary_list DUY NHẤT 1 LẦN (CDR_DT_ID &lt;= :DATADT đã bao trùm cả
+-- ngày hiện tại và ngày làm việc trước, vì wd_int luôn &lt; DATADT) - dùng lại cho cả
+-- lsl_latest/lsl_same_day/lsl_prev và CTE pastdue_prev bên dưới, thay vì đọc 4 lần.
+lsl_snap AS (
+    SELECT LD_NO, CDR_DT_ID, CIF, BRANCH_CODE, CURRENCY, LOAN_CLASSIFICATION,
+           INTERATE_RATE, TOTAL_AMOUNT, TOTAL_AMOUNT_EQ
+    FROM   loan_summary_list
+    WHERE  CDR_DT_ID &lt;= CAST(:DATADT AS INT)
+),
+lsl_latest AS (
+    SELECT LD_NO,
+           max_by(CIF,                 CDR_DT_ID) AS CIF,
+           max_by(BRANCH_CODE,         CDR_DT_ID) AS BRANCH_CODE,
+           max_by(CURRENCY,            CDR_DT_ID) AS CURRENCY,
+           max_by(LOAN_CLASSIFICATION, CDR_DT_ID) AS LOAN_CLASSIFICATION,
+           max_by(INTERATE_RATE,       CDR_DT_ID) AS INTERATE_RATE
+    FROM   lsl_snap
+    GROUP BY LD_NO
+),
+lsl_same_day AS (
+    SELECT LD_NO,
+           max_by(TOTAL_AMOUNT,    CDR_DT_ID) AS TOTAL_AMOUNT,
+           max_by(TOTAL_AMOUNT_EQ, CDR_DT_ID) AS TOTAL_AMOUNT_EQ
+    FROM   lsl_snap
+    WHERE  CDR_DT_ID = CAST(:DATADT AS INT)
+    GROUP BY LD_NO
+),
+lsl_prev AS (
+    SELECT l.LD_NO,
+           max_by(l.LOAN_CLASSIFICATION, l.CDR_DT_ID) AS ln_cls_d_1
+    FROM   lsl_snap l, prev_wd w
+    WHERE  l.CDR_DT_ID = w.wd_int
+    GROUP BY l.LD_NO
+),
+pd_raw AS (
+    SELECT h.loans_payment_due_hashkey, h.business_key AS id,
+           ov.t_pay_type, ov.t_pay_amt_outs, inf.t_payment_dte_due
+    FROM      pd_active   h
+    LEFT JOIN sat_pd_over ov  ON ov.loans_payment_due_hashkey  = h.loans_payment_due_hashkey
+    LEFT JOIN sat_pd_info inf ON inf.loans_payment_due_hashkey = h.loans_payment_due_hashkey
+),
+pd_l1 AS (
+    SELECT id, e1.sub_id,
+           e1.pay_type_grp                          AS pay_type_grp,
+           SPLIT(t_payment_dte_due,'::')[e1.sub_id] AS dte_due,
+           SPLIT(t_pay_amt_outs,'::')[e1.sub_id]    AS amt_outs_grp
+    FROM   pd_raw
+    LATERAL VIEW POSEXPLODE(SPLIT(t_pay_type,'::')) e1 AS sub_id, pay_type_grp
+),
+pd_sv AS (
+    SELECT id, SUBSTR(id, -12) AS ld_no, sub_id, e2.sv_id,
+           e2.t_pay_type                      AS t_pay_type,
+           dte_due                            AS t_payment_dte_due,
+           SPLIT(amt_outs_grp,'!!')[e2.sv_id] AS t_pay_amt_outs
+    FROM   pd_l1
+    LATERAL VIEW POSEXPLODE(SPLIT(pay_type_grp,'!!')) e2 AS sv_id, t_pay_type
+    WHERE  NVL(CAST(NULLIF(SPLIT(amt_outs_grp,'!!')[e2.sv_id],'') AS DECIMAL(30,4)), 0) &lt;&gt; 0
+),
+pastdue_prev AS (
+    SELECT s.ld_no,
+           -- MIN(CASE...ELSE NULL END): conditional MIN có chủ đích - NULL khi không khớp
+           -- pay_type để MIN() bỏ qua, không phải thiếu nhánh ELSE.
+           COALESCE(DATEDIFF(TO_DATE(CAST(w.wd_int AS STRING),'yyyyMMdd'),
+                    MIN(CASE WHEN s.t_pay_type = 'PR'
+                             THEN TO_DATE(s.t_payment_dte_due,'yyyyMMdd') ELSE NULL END)), 0) AS max_days_pd_pr,
+           COALESCE(DATEDIFF(TO_DATE(CAST(w.wd_int AS STRING),'yyyyMMdd'),
+                    MIN(CASE WHEN s.t_pay_type = 'IN'
+                             THEN TO_DATE(s.t_payment_dte_due,'yyyyMMdd') ELSE NULL END)), 0) AS max_days_pd_in
+    FROM   pd_sv s
+           CROSS JOIN prev_wd w
+           JOIN ( SELECT DISTINCT l.LD_NO
+                  FROM   lsl_snap l, prev_wd w2
+                  WHERE  l.CDR_DT_ID = w2.wd_int ) lk ON lk.LD_NO = s.ld_no
+    GROUP BY s.ld_no, w.wd_int
+),
+lt AS (
+    SELECT
+        a.ld_no                       AS LD_NO,
+        a.tk_thuno                    AS TK_THUNO,
+        b.CIF                         AS CIF,
+        c.MACN_QL                     AS BRANCH_PARENT_CODE,
+        c.TENCN_QL                    AS BRANCH_PARENT_NAME,
+        c.MACN                        AS BRANCH_CODE,
+        c.TENCN                       AS BRANCH_NAME,
+        d.full_name                   AS FULL_NAME,
+        d3.custgroup_description      AS CUSTGROUP_DESCRIPTION,
+        NVL(sd.TOTAL_AMOUNT,0)        AS TOTAL_AMOUNT,
+        NVL(sd.TOTAL_AMOUNT_EQ,0)     AS TOTAL_AMOUNT_EQ,
+        b.CURRENCY                    AS CURRENCY,
+        b.LOAN_CLASSIFICATION         AS LOAN_CLASSIFICATION,
+        b.INTERATE_RATE               AS INTERATE_RATE,
+        a.thoailaiduthu               AS THOAILAIDUTHU,
+        a.thu_goc                     AS THU_GOC,
+        a.thu_in                      AS THU_IN,
+        a.thu_pe                      AS THU_PE,
+        a.thu_ps                      AS THU_PS,
+        a.thu_phi                     AS THU_PHI,
+        pd.max_days_pd_pr             AS PDDAYS_PR_D_1,
+        pd.max_days_pd_in             AS PDDAYS_IN_D_1,
+        lp.ln_cls_d_1                 AS LN_CLS_D_1
+    FROM      thu          a
+    LEFT JOIN lsl_latest   b  ON b.LD_NO  = a.ld_no
+    LEFT JOIN lsl_same_day sd ON sd.LD_NO = a.ld_no
+    LEFT JOIN br_raw       c  ON CAST(c.MACN AS STRING) = CAST(b.BRANCH_CODE AS STRING)
+    LEFT JOIN cust_name    d  ON CAST(d.cif  AS STRING) = CAST(b.CIF AS STRING)
+    LEFT JOIN cust_grp     d3 ON CAST(d3.cif AS STRING) = CAST(b.CIF AS STRING)
+    LEFT JOIN pastdue_prev pd ON pd.ld_no = a.ld_no
+    LEFT JOIN lsl_prev     lp ON lp.LD_NO = a.ld_no
+),
+ld AS (
+    SELECT h.business_key   AS id,
+           hc.business_key  AS t_customer_id,
+           hb.business_key  AS t_co_code,
+           tm.t_value_date
+    FROM      loans_active       h
+    LEFT JOIN lnk_loans_customer lc ON lc.loans_hashkey    = h.loans_hashkey
+    LEFT JOIN customer_active    hc ON hc.customer_hashkey = lc.customer_hashkey
+    LEFT JOIN lnk_loans_branch   lb ON lb.loans_hashkey    = h.loans_hashkey
+    LEFT JOIN branch_active      hb ON hb.branch_hashkey   = lb.branch_hashkey
+    LEFT JOIN sat_ld_terms       tm ON tm.loans_hashkey    = h.loans_hashkey
+),
+bcn085 AS (
+    SELECT
+        TO_DATE(:DATADT,'yyyyMMdd')                                  AS DATA_DATE,
+        COALESCE(A.CIF,                   B.t_customer_id)           AS MA_KH,
+        COALESCE(A.BRANCH_PARENT_CODE,    BR.MACN_QL)                AS MACN_QL,
+        COALESCE(A.BRANCH_PARENT_NAME,    BR.TENCN_QL)               AS TENCN_QL,
+        COALESCE(A.BRANCH_CODE,           B.t_co_code)               AS MACN,
+        COALESCE(A.BRANCH_NAME,           BR.TENCN)                  AS TENCN,
+        COALESCE(A.FULL_NAME,             CCN.full_name)             AS TEN_KHACH_HANG,
+        COALESCE(A.CUSTGROUP_DESCRIPTION, CCG.custgroup_description) AS TEN_KHOI_PHAN_KHUC,
+        A.LD_NO,
+        A.TK_THUNO                                                   AS TK_THUNO,
+        A.TOTAL_AMOUNT                                               AS DU_NO_NGUYEN_TE,
+        A.TOTAL_AMOUNT_EQ                                            AS DU_NO_QUY_DOI_VND,
+        A.CURRENCY                                                   AS MA_TIEN_TE,
+        A.LOAN_CLASSIFICATION                                        AS NHOM_NO,
+        A.INTERATE_RATE                                              AS LAI_SUAT,
+        A.THOAILAIDUTHU, A.THU_GOC, A.THU_IN, A.THU_PE, A.THU_PS, A.THU_PHI,
+        A.PDDAYS_PR_D_1                                              AS PR_DAY,
+        A.PDDAYS_IN_D_1                                              AS IN_DAY,
+        A.LN_CLS_D_1                                                 AS NHOM_NO_D_1,
+        B.t_value_date                                               AS NGAYGIAINGAN
+    FROM      lt A
+    LEFT JOIN ld      B   ON CAST(B.id     AS STRING) = CAST(A.LD_NO AS STRING)
+    LEFT JOIN br_raw  BR  ON CAST(BR.MACN  AS STRING) = CAST(B.t_co_code AS STRING)
+    LEFT JOIN cust_name CCN ON CAST(CCN.cif AS STRING) = CAST(B.t_customer_id AS STRING)
+    LEFT JOIN cust_grp  CCG ON CAST(CCG.cif AS STRING) = CAST(B.t_customer_id AS STRING)
+)
+SELECT
+    -- ROWNUM: cột kỹ thuật đánh số thứ tự dòng theo DATA_DATE (giữ nguyên hành vi code cũ),
+    -- KHÔNG phải pattern "lấy bản ghi mới nhất" nên không thay được bằng MAX_BY.
+    ROW_NUMBER() OVER (ORDER BY DATA_DATE)      AS ROWNUM,
+    THOAILAIDUTHU                               AS THOAILAIDUTHU,
+    MACN_QL                                     AS BRANCH_PARENT_CODE,
+    DATE_FORMAT(DATA_DATE,'yyyyMMdd')           AS DATA_DATE,
+    DU_NO_QUY_DOI_VND                           AS TOTAL_AMOUNT_EQ,
+    THU_PS                                      AS THU_PS,
+    TEN_KHACH_HANG                              AS FULL_NAME,
+    MACN                                        AS BRANCH_CODE,
+    PR_DAY                                      AS PDDAYS_PR_D_1,
+    IN_DAY                                      AS PDDAYS_IN_D_1,
+    LAI_SUAT                                    AS INTERATE_RATE,
+    MA_TIEN_TE                                  AS CURRENCY,
+    MA_KH                                       AS CIF,
+    NHOM_NO_D_1                                 AS LN_CLS_D_1,
+    THU_PE                                      AS THU_PE,
+    LD_NO                                       AS LD_NO,
+    TK_THUNO                                    AS TK_THUNO,
+    THU_PHI                                     AS THU_PHI,
+    TENCN_QL                                    AS BRANCH_PARENT_NAME,
+    NGAYGIAINGAN                                AS NGAY_GIAI_NGAN,
+    THU_IN                                      AS THU_IN,
+    TENCN                                       AS BRANCH_NAME,
+    CAST(NHOM_NO AS DECIMAL(1,0))               AS LOAN_CLASSIFICATION,
+    TEN_KHOI_PHAN_KHUC                          AS CUSTGROUP_DESCRIPTION,
+    DU_NO_NGUYEN_TE                             AS TOTAL_AMOUNT,
+    THU_GOC                                     AS THU_GOC
+FROM   bcn085
+;
+</t>
+  </si>
+  <si>
+    <t>USE CATALOG IDENTIFIER(:curated);
+USE SCHEMA tckh;
+CREATE OR REPLACE VIEW v_bcn_thuno_1 AS
+WITH
+-- ── BCN085: chi tiết thu nợ, enrich CUST_GROUP từ t24_customer theo DATA_DATE + CIF
+bcn085 AS (
+    SELECT
+        a.DATA_DATE,
+        eomonth(dateadd(month, -1, eomonth(a.DATA_DATE)))  AS BOM,
+        a.CIF,
+        a.FULL_NAME,
+        a.BRANCH_CODE,
+        a.BRANCH_NAME,
+        a.BRANCH_PARENT_CODE,
+        a.BRANCH_PARENT_NAME,
+        a.LD_NO,
+        a.LOAN_CLASSIFICATION,
+        REPLACE(a.TK_THUNO, '''', '')                      AS TK_THUNO,
+        a.THU_GOC, a.THU_IN, a.THU_PE, a.THU_PS, a.THU_PHI,
+        a.LN_CLS_D_1,
+        a.INTERATE_RATE,
+        ISNULL(a.PDDAYS_IN_D_1, 0)                          AS PDDAYS_IN_D_1,
+        ISNULL(a.PDDAYS_PR_D_1, 0)                          AS PDDAYS_PR_D_1,
+        a.THOAILAIDUTHU,
+        a.CUSTGROUP_DESCRIPTION,
+        b.T_CUST_GROUP                                      AS T_CUST_GROUP
+    FROM      tb_bcn085_thuno_dtl a
+    LEFT JOIN t24_customer b
+           ON a.DATA_DATE = b.DATA_DATE
+          AND a.CIF       = b.ID
+    WHERE a.DATA_DATE &gt;= '20260101' AND a.DATA_DATE &lt;= '20991231'
+),
+-- ── Sao kê BCN085 kèm nhóm nợ CIC (từ d_cic_dungky_final)
+saoke AS (
+    SELECT
+        s.DATA_DATE,
+        eomonth(s.DATA_DATE)                     AS EOM,
+        s.CIF,
+        s.FULL_NAME,
+        s.BRANCH_CODE,
+        s.LD_NO,
+        s.NHOM_NO_QUANTRI_V2,
+        cic.NN_TT31_KEOTHEO_CIC                  AS NHOM_NO_cic,
+        s.NHOM_NO_CANDOI,
+        s.NHOM_NO_THEO_SNQH,
+        s.SO_NGAY_QH_GOC,
+        s.SO_NGAY_QH_LAI,
+        s.DUNO_NTE,
+        s.DUNO_QUYVND
+    FROM      tb_saoke_bcn085 s
+    LEFT JOIN d_cic_dungky_final cic
+           ON s.CIF       = cic.CIF
+          AND s.DATA_DATE = cic.NGAY
+          AND s.LD_NO     = cic.SO_HOP_DONG
+    WHERE s.DATA_DATE &gt;= 20251231
+),
+-- ── Nhóm nợ CIC theo CIF (gộp theo mọi LD_NO), lấy giá trị lớn nhất
+nhomno_cic AS (
+    SELECT
+        s.DATA_DATE,
+        eomonth(s.DATA_DATE)                       AS EOM,
+        s.CIF,
+        MAX(cic.NN_TT31_KEOTHEO_CIC)               AS NHOM_NO_cic
+    FROM      tb_saoke_bcn085 s
+    LEFT JOIN d_cic_dungky_final cic
+           ON s.CIF       = cic.CIF
+          AND s.DATA_DATE = cic.NGAY
+          AND s.LD_NO     = cic.SO_HOP_DONG
+    WHERE s.DATA_DATE &gt;= 20251231
+    GROUP BY s.DATA_DATE, eomonth(s.DATA_DATE), s.CIF
+),
+-- ── Sao kê đầu năm (mốc 20251231), dùng làm số dư/nhóm nợ đầu kỳ
+saoke_dau_nam AS (
+    SELECT
+        DATA_DATE, eomonth(DATA_DATE) AS EOM, CIF, FULL_NAME, BRANCH_CODE, LD_NO,
+        NHOM_NO_QUANTRI_V2, NHOM_NO_cic, NHOM_NO_CANDOI, NHOM_NO_THEO_SNQH,
+        SO_NGAY_QH_GOC, SO_NGAY_QH_LAI, DUNO_NTE, DUNO_QUYVND
+    FROM tb_saoke_bcn085
+    WHERE DATA_DATE = 20251231
+)
+SELECT
+    a.DATA_DATE,
+    a.DATA_DATE                                                 AS CDR_DT_ID,
+    a.BOM,
+    a.CIF,
+    a.FULL_NAME,
+    a.BRANCH_CODE,
+    a.BRANCH_NAME,
+    a.BRANCH_PARENT_CODE,
+    a.BRANCH_PARENT_NAME,
+    a.LD_NO,
+    a.LOAN_CLASSIFICATION,
+    a.TK_THUNO,
+    a.THU_GOC,
+    a.THU_IN,
+    a.THU_PE,
+    a.THU_PS,
+    a.THU_PHI,
+    a.LN_CLS_D_1,
+    a.INTERATE_RATE,
+    a.PDDAYS_IN_D_1,
+    a.PDDAYS_PR_D_1,
+    a.THOAILAIDUTHU,
+    b.NHOM_NO_QUANTRI_V2,
+    ISNULL(cic.NHOM_NO_cic, b.NHOM_NO_cic)                      AS NHOM_NO_CIC,
+    b.NHOM_NO_CANDOI,
+    b.NHOM_NO_THEO_SNQH,
+    b.SO_NGAY_QH_GOC,
+    b.SO_NGAY_QH_LAI,
+    b.DUNO_NTE,
+    b.DUNO_QUYVND,
+    a.CUSTGROUP_DESCRIPTION,
+    a.T_CUST_GROUP,
+    dau_nam.NHOM_NO_THEO_SNQH                                   AS NHOM_NO_THEO_SNQH_DAUNAM,
+    dau_nam.NHOM_NO_cic                                         AS NHOM_NO_CIC_DAU_NAM,
+    dau_nam.NHOM_NO_QUANTRI_V2                                  AS NHOM_NO_QUANTRI_V2_DAUNAM
+FROM      bcn085 a
+LEFT JOIN saoke          b       ON a.LD_NO = b.LD_NO AND a.BOM = b.EOM
+LEFT JOIN nhomno_cic     cic     ON a.CIF   = cic.CIF AND a.BOM = cic.EOM
+LEFT JOIN saoke_dau_nam  dau_nam ON a.LD_NO = dau_nam.LD_NO
+WHERE a.DATA_DATE &gt;= '20251231' AND a.DATA_DATE &lt;= '20261231';</t>
+  </si>
+  <si>
+    <t>tb_ar_bcn_dtl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
+USE SCHEMA tckh;
+DELETE FROM tb_ar_bcn_dtl
+WHERE  CDR_DT_ID = CAST(:DATADT AS INT);
+INSERT INTO tb_ar_bcn_dtl
+    (CDR_DT_ID, DATA_DATE, LD_NO, BRANCH_CODE,
+     INDUSTRY_LEV5, INDUSTRY_LEV5_DSC, INDUSTRY_LEV4, INDUSTRY_LEV4_DSC,
+     PRO_BUNDLE, PROD_MAIN)
+WITH
+loans_sts_del AS (
+    SELECT loans_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sts_hub_loans')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY loans_hashkey
+    HAVING max_by(cdc_status, source_event_date) = 'D'
+),
+loans_hub AS (
+    SELECT loans_hashkey, business_key
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.hub_loans')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+      AND  (business_key LIKE 'LD%' OR business_key LIKE 'PDLD%')
+    GROUP BY loans_hashkey, business_key
+),
+loans_active AS (
+    SELECT h.loans_hashkey, h.business_key
+    FROM      loans_hub h
+    LEFT JOIN loans_sts_del x ON x.loans_hashkey = h.loans_hashkey
+    WHERE  x.loans_hashkey IS NULL
+),
+branch_sts_del AS (
+    SELECT branch_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sts_hub_branch')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY branch_hashkey
+    HAVING max_by(cdc_status, source_event_date) = 'D'
+),
+branch_hub AS (
+    SELECT branch_hashkey, business_key
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.hub_branch')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY branch_hashkey, business_key
+),
+branch_active AS (
+    SELECT h.branch_hashkey, h.business_key
+    FROM      branch_hub h
+    LEFT JOIN branch_sts_del x ON x.branch_hashkey = h.branch_hashkey
+    WHERE  x.branch_hashkey IS NULL
+),
+lnk_loans_branch AS (
+    SELECT loans_hashkey,
+           max_by(branch_hashkey, source_event_date) AS branch_hashkey
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.link_loans_branch')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY loans_hashkey
+),
+class_raw AS (
+    SELECT loans_hashkey,
+           max_by(t_industry_lev3,   source_event_date) AS t_industry_lev3,
+           max_by(t_ocb_pro_bundle,  source_event_date) AS t_ocb_pro_bundle,
+           max_by(t_ocb_prod_main,   source_event_date) AS t_ocb_prod_main
+    FROM   IDENTIFIER(:cleaned || '.raw_vault.sat_loans_classification')
+    WHERE  source_event_date &lt;= TO_DATE(:DATADT,'yyyyMMdd')
+    GROUP BY loans_hashkey
+),
+class_latest AS (
+    SELECT loans_hashkey, t_industry_lev3, t_ocb_pro_bundle, t_ocb_prod_main,
+           CASE WHEN t_industry_lev3 RLIKE '^[A-Za-z]' AND LENGTH(t_industry_lev3) &gt;= 6
+                THEN SUBSTR(t_industry_lev3, 1, 6) ELSE NULL END AS industry_lev5_code,
+           CASE WHEN t_industry_lev3 RLIKE '^[A-Za-z]' AND LENGTH(t_industry_lev3) &gt;= 5
+                THEN SUBSTR(t_industry_lev3, 1, 5) ELSE NULL END AS industry_lev4_code
+    FROM class_raw
+)
+SELECT
+    CAST(:DATADT AS INT)                          AS CDR_DT_ID,
+    TO_DATE(:DATADT,'yyyyMMdd')                   AS DATA_DATE,
+    h.business_key                                AS LD_NO,
+    bh.business_key                                AS BRANCH_CODE,
+    cl.industry_lev5_code                         AS INDUSTRY_LEV5,
+    r5.ref_description                            AS INDUSTRY_LEV5_DSC,
+    cl.industry_lev4_code                         AS INDUSTRY_LEV4,
+    r4.ref_description                            AS INDUSTRY_LEV4_DSC,
+    cl.t_ocb_pro_bundle                           AS PRO_BUNDLE,
+    cl.t_ocb_prod_main                            AS PROD_MAIN
+FROM loans_active h
+LEFT JOIN class_latest      cl ON cl.loans_hashkey = h.loans_hashkey
+LEFT JOIN lnk_loans_branch  lb ON lb.loans_hashkey = h.loans_hashkey
+LEFT JOIN branch_active     bh ON bh.branch_hashkey = lb.branch_hashkey
+LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.ref_t24_ld_economic_sector') r5
+       ON r5.ref_code = cl.industry_lev5_code
+LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.ref_t24_ld_economic_sector') r4
+       ON r4.ref_code = cl.industry_lev4_code
+;
+</t>
+  </si>
+  <si>
+    <t>USE CATALOG IDENTIFIER(:curated);
+USE SCHEMA tckh;
+DELETE FROM T24_CUSTOMER
+WHERE DATA_DATE = :DATADT;
+INSERT INTO T24_CUSTOMER
+WITH
+cust_sts_del AS (
+    SELECT customer_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_customer')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    GROUP BY customer_hashkey
+    HAVING max_by(cdc_status, source_event_date) = 'D'
+),
+cust_active AS (
+    SELECT
+        h.customer_hashkey,
+        h.business_key,
+        h.source_event_date
+    FROM IDENTIFIER(:cleaned || '.raw_vault.hub_customer') h
+    LEFT JOIN cust_sts_del d ON d.customer_hashkey = h.customer_hashkey
+    WHERE d.customer_hashkey IS NULL
+      AND h.source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+      AND h.record_source = 't24__t24_customer'
+),
+cust_other AS (
+    SELECT
+        customer_hashkey,
+        max_by(contact_date, source_event_date) AS contact_date,
+        max_by(province,     source_event_date) AS province,
+        max_by(fax_1,        source_event_date) AS fax_1,
+        max_by(email_2,      source_event_date) AS email_2
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_customer_other')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    GROUP BY customer_hashkey
+),
+cust_branch_cur AS (
+    SELECT
+        customer_hashkey,
+        max_by(branch_hashkey, source_event_date) AS branch_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_customer_branch')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    GROUP BY customer_hashkey
+),
+cust_branch AS (
+    SELECT
+        l.customer_hashkey,
+        hb.business_key AS company_book
+    FROM cust_branch_cur l
+    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_branch') hb
+        ON l.branch_hashkey = hb.branch_hashkey
+),
+cust_officer_cur AS (
+    SELECT
+        customer_hashkey,
+        max_by(dept_acct_officer_hashkey, source_event_date) AS dept_acct_officer_hashkey
+    FROM IDENTIFIER(:cleaned || '.raw_vault.link_customer_dept_acct_officer_nvql')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    GROUP BY customer_hashkey
+),
+cust_officer AS (
+    SELECT
+        l.customer_hashkey,
+        ha.business_key AS account_officer
+    FROM cust_officer_cur l
+    JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_acct_officer') ha
+        ON l.dept_acct_officer_hashkey = ha.dept_acct_officer_hashkey
+)
+SELECT
+    hub.customer_hashkey                                           AS IP_ID,
+    hub.business_key                                               AS ID,
+    DATE_FORMAT(pit.snapshot_date, 'yyyyMMdd')                     AS DATA_DATE,
+    si.short_name                                                  AS T_SHORT_NAME,
+    si.language                                                    AS T_LANGUAGE,
+    TO_CHAR(TO_DATE(si.create_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8)      AS T_CREATE_DATE,
+    si.education_level                                             AS T_EDUCATION_LEVEL,
+    si.job_title                                                   AS T_JOB_TITLE,
+    si.occupation                                                  AS T_OCCUPATION,
+    si.marital_status                                              AS T_MARITAL_STATUS,
+    si.labour_number                                               AS T_LABOUR_NUMBER,
+    si.gender                                                      AS T_GENDER,
+    TO_CHAR(TO_DATE(si.birth_incorp_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8) AS T_BIRTH_INCORP_DATE,
+    si.residence                                                   AS T_RESIDENCE,
+    si.nationality                                                 AS T_NATIONALITY,
+    sc.address                                                     AS T_ADDRESS,
+    sc.town_country                                                AS T_TOWN_COUNTRY,
+    sc.province_1                                                  AS T_PROVINCE_1,
+    sc.phone_1                                                     AS T_PHONE_1,
+    sc.sms_1                                                       AS T_SMS_1,
+    sc.off_phone                                                   AS T_OFF_PHONE,
+    sc.email_1                                                     AS T_EMAIL_1,
+    sc.province_2                                                  AS T_PROVINCE_2,
+    sc.town_country_2                                              AS T_TOWN_COUNTRY_2,
+    sc.sms_2                                                       AS T_SMS_2,
+    sc.phone_2                                                     AS T_PHONE_2,
+    sc.off_phone_2                                                 AS T_OFF_PHONE_2,
+    scl.sector                                                     AS T_SECTOR,
+    scl.industry                                                   AS T_INDUSTRY,
+    scl.cust_group                                                 AS T_CUST_GROUP,
+    sk.tax_id                                                      AS T_TAX_ID,
+    sk.legal_id                                                    AS T_LEGAL_ID,
+    sk.legal_doc_name                                              AS T_LEGAL_DOC_NAME,
+    TO_CHAR(TO_DATE(so.contact_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8)      AS T_CONTACT_DATE,
+    so.province                                                    AS T_PROVINCE,
+    so.fax_1                                                       AS T_FAX_1,
+    so.email_2                                                     AS T_EMAIL_2,
+    sf.net_monthly_in                                              AS T_NET_MONTHLY_IN,
+    sf.total_property                                              AS T_TOTAL_PROPERTY,
+    sf.total_income                                                AS T_TOTAL_INCOME,
+    cb.company_book                                                AS T_COMPANY_BOOK,
+    ao.account_officer                                             AS T_ACCOUNT_OFFICER
+FROM IDENTIFIER(:cleaned || '.business_vault.pit_customer') pit
+LEFT JOIN cust_active hub
+    ON pit.customer_hashkey = hub.customer_hashkey
+LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_customer_information') si
+    ON  si.customer_hashkey  = pit.customer_hashkey
+    AND si.source_event_date = pit.sat_customer_information_src_ev_dt
+LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_customer_contact') sc
+    ON  sc.customer_hashkey  = pit.customer_hashkey
+    AND sc.source_event_date = pit.sat_customer_contact_src_ev_dt
+LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_customer_classification') scl
+    ON  scl.customer_hashkey  = pit.customer_hashkey
+    AND scl.source_event_date = pit.sat_customer_classification_src_ev_dt
+LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_customer_kyc') sk
+    ON  sk.customer_hashkey  = pit.customer_hashkey
+    AND sk.source_event_date = pit.sat_customer_kyc_src_ev_dt
+LEFT JOIN cust_other so
+    ON so.customer_hashkey = hub.customer_hashkey
+LEFT JOIN IDENTIFIER(:cleaned || '.raw_vault.sat_customer_financial_statement') sf
+    ON  sf.customer_hashkey  = pit.customer_hashkey
+    AND sf.source_event_date = pit.sat_customer_financial_statement_src_ev_dt
+LEFT JOIN cust_branch cb
+    ON cb.customer_hashkey = hub.customer_hashkey
+LEFT JOIN cust_officer ao
+    ON ao.customer_hashkey = hub.customer_hashkey;</t>
+  </si>
+  <si>
     <t>JOIN SCHEMA</t>
   </si>
   <si>
@@ -609,7 +1395,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -718,6 +1504,25 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -793,7 +1598,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -1132,11 +1937,59 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1226,6 +2079,22 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1283,8 +2152,8 @@
     <xf numFmtId="0" fontId="14" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1326,6 +2195,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1710,7 +2582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V90"/>
+  <dimension ref="A1:V91"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1731,1387 +2603,1439 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="27.95" customHeight="1">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="47"/>
-      <c r="O1" s="47"/>
-      <c r="P1" s="47"/>
-      <c r="Q1" s="47"/>
-      <c r="R1" s="47"/>
-      <c r="S1" s="47"/>
-      <c r="T1" s="47"/>
-      <c r="U1" s="47"/>
-      <c r="V1" s="47"/>
-    </row>
-    <row r="3" spans="1:22" ht="29.1">
-      <c r="A3" s="1" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
+      <c r="S1" s="55"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
+    </row>
+    <row r="3" spans="1:22" ht="29.1" customHeight="1">
+      <c r="A3" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="B3" s="64"/>
+      <c r="D3" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="E3" s="64"/>
+      <c r="G3" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="L3" s="64" t="s">
         <v>4</v>
       </c>
-    </row>
+      <c r="M3" s="64"/>
+      <c r="N3" s="64"/>
+      <c r="O3" s="64"/>
+      <c r="Q3" s="64" t="s">
+        <v>5</v>
+      </c>
+      <c r="R3" s="64"/>
+      <c r="S3" s="64"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="1"/>
+    </row>
+    <row r="4" spans="1:22" ht="15"/>
     <row r="5" spans="1:22" ht="14.45" customHeight="1">
-      <c r="A5" s="58" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="58"/>
-      <c r="D5" s="58" t="s">
+      <c r="A5" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="58"/>
-      <c r="G5" s="48" t="s">
+      <c r="B5" s="66"/>
+      <c r="D5" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="L5" s="56" t="s">
+      <c r="E5" s="66"/>
+      <c r="G5" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
-      <c r="Q5" s="37" t="s">
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="L5" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="R5" s="37"/>
-      <c r="S5" s="37"/>
-      <c r="T5" s="37"/>
+      <c r="M5" s="79"/>
+      <c r="N5" s="79"/>
+      <c r="O5" s="79"/>
+      <c r="Q5" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="R5" s="45"/>
+      <c r="S5" s="45"/>
+      <c r="T5" s="45"/>
     </row>
     <row r="6" spans="1:22" ht="18.600000000000001" customHeight="1">
-      <c r="A6" s="59"/>
-      <c r="B6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="50"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="39"/>
+      <c r="A6" s="67"/>
+      <c r="B6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+      <c r="O6" s="58"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="47"/>
     </row>
     <row r="7" spans="1:22" ht="14.45" customHeight="1">
-      <c r="A7" s="59"/>
-      <c r="B7" s="59"/>
-      <c r="D7" s="59"/>
-      <c r="E7" s="59"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="50"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
-      <c r="T7" s="39"/>
+      <c r="A7" s="67"/>
+      <c r="B7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="L7" s="58"/>
+      <c r="M7" s="58"/>
+      <c r="N7" s="58"/>
+      <c r="O7" s="58"/>
+      <c r="Q7" s="47"/>
+      <c r="R7" s="47"/>
+      <c r="S7" s="47"/>
+      <c r="T7" s="47"/>
     </row>
     <row r="8" spans="1:22" ht="14.45" customHeight="1">
-      <c r="A8" s="59"/>
-      <c r="B8" s="59"/>
-      <c r="D8" s="59"/>
-      <c r="E8" s="59"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="50"/>
-      <c r="Q8" s="39"/>
-      <c r="R8" s="39"/>
-      <c r="S8" s="39"/>
-      <c r="T8" s="39"/>
+      <c r="A8" s="67"/>
+      <c r="B8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="57"/>
+      <c r="L8" s="58"/>
+      <c r="M8" s="58"/>
+      <c r="N8" s="58"/>
+      <c r="O8" s="58"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="47"/>
+      <c r="T8" s="47"/>
     </row>
     <row r="9" spans="1:22" ht="18.600000000000001" customHeight="1">
-      <c r="A9" s="59"/>
-      <c r="B9" s="59"/>
-      <c r="D9" s="59"/>
-      <c r="E9" s="59"/>
+      <c r="A9" s="67"/>
+      <c r="B9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
       <c r="F9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
-      <c r="L9" s="50"/>
-      <c r="M9" s="50"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="50"/>
-      <c r="Q9" s="39"/>
-      <c r="R9" s="39"/>
-      <c r="S9" s="39"/>
-      <c r="T9" s="39"/>
+        <v>11</v>
+      </c>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="57"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="58"/>
+      <c r="N9" s="58"/>
+      <c r="O9" s="58"/>
+      <c r="Q9" s="47"/>
+      <c r="R9" s="47"/>
+      <c r="S9" s="47"/>
+      <c r="T9" s="47"/>
     </row>
     <row r="10" spans="1:22" ht="14.45" customHeight="1">
-      <c r="A10" s="59"/>
-      <c r="B10" s="59"/>
-      <c r="D10" s="59"/>
-      <c r="E10" s="59"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="50"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="50"/>
-      <c r="Q10" s="39"/>
-      <c r="R10" s="39"/>
-      <c r="S10" s="39"/>
-      <c r="T10" s="39"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="L10" s="58"/>
+      <c r="M10" s="58"/>
+      <c r="N10" s="58"/>
+      <c r="O10" s="58"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="47"/>
+      <c r="S10" s="47"/>
+      <c r="T10" s="47"/>
     </row>
     <row r="11" spans="1:22" ht="14.45" customHeight="1">
-      <c r="A11" s="59"/>
-      <c r="B11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="49"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
-      <c r="L11" s="50"/>
-      <c r="M11" s="50"/>
-      <c r="N11" s="50"/>
-      <c r="O11" s="50"/>
+      <c r="A11" s="67"/>
+      <c r="B11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="L11" s="58"/>
+      <c r="M11" s="58"/>
+      <c r="N11" s="58"/>
+      <c r="O11" s="58"/>
       <c r="P11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q11" s="39"/>
-      <c r="R11" s="39"/>
-      <c r="S11" s="39"/>
-      <c r="T11" s="39"/>
+        <v>11</v>
+      </c>
+      <c r="Q11" s="47"/>
+      <c r="R11" s="47"/>
+      <c r="S11" s="47"/>
+      <c r="T11" s="47"/>
     </row>
     <row r="12" spans="1:22" ht="14.45" customHeight="1">
-      <c r="A12" s="59"/>
-      <c r="B12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="59"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="49"/>
-      <c r="I12" s="49"/>
-      <c r="J12" s="49"/>
-      <c r="L12" s="50"/>
-      <c r="M12" s="50"/>
-      <c r="N12" s="50"/>
-      <c r="O12" s="50"/>
-      <c r="Q12" s="39"/>
-      <c r="R12" s="39"/>
-      <c r="S12" s="39"/>
-      <c r="T12" s="39"/>
+      <c r="A12" s="67"/>
+      <c r="B12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="57"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="58"/>
+      <c r="N12" s="58"/>
+      <c r="O12" s="58"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="47"/>
+      <c r="T12" s="47"/>
     </row>
     <row r="13" spans="1:22" ht="14.45" customHeight="1">
-      <c r="A13" s="59"/>
-      <c r="B13" s="59"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="59"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="L13" s="50"/>
-      <c r="M13" s="50"/>
-      <c r="N13" s="50"/>
-      <c r="O13" s="50"/>
-      <c r="Q13" s="39"/>
-      <c r="R13" s="39"/>
-      <c r="S13" s="39"/>
-      <c r="T13" s="39"/>
+      <c r="A13" s="67"/>
+      <c r="B13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
+      <c r="J13" s="57"/>
+      <c r="L13" s="58"/>
+      <c r="M13" s="58"/>
+      <c r="N13" s="58"/>
+      <c r="O13" s="58"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="47"/>
+      <c r="T13" s="47"/>
     </row>
     <row r="14" spans="1:22" ht="14.45" customHeight="1">
-      <c r="A14" s="59"/>
-      <c r="B14" s="59"/>
-      <c r="D14" s="59"/>
-      <c r="E14" s="59"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
-      <c r="L14" s="50"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="50"/>
-      <c r="O14" s="50"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="39"/>
-      <c r="S14" s="39"/>
-      <c r="T14" s="39"/>
+      <c r="A14" s="67"/>
+      <c r="B14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="57"/>
+      <c r="L14" s="58"/>
+      <c r="M14" s="58"/>
+      <c r="N14" s="58"/>
+      <c r="O14" s="58"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="47"/>
+      <c r="S14" s="47"/>
+      <c r="T14" s="47"/>
     </row>
     <row r="15" spans="1:22" ht="14.45" customHeight="1">
-      <c r="A15" s="59"/>
-      <c r="B15" s="59"/>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="49"/>
+      <c r="A15" s="67"/>
+      <c r="B15" s="67"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
       <c r="K15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L15" s="50"/>
-      <c r="M15" s="50"/>
-      <c r="N15" s="50"/>
-      <c r="O15" s="50"/>
-      <c r="Q15" s="39"/>
-      <c r="R15" s="39"/>
-      <c r="S15" s="39"/>
-      <c r="T15" s="39"/>
+        <v>11</v>
+      </c>
+      <c r="L15" s="58"/>
+      <c r="M15" s="58"/>
+      <c r="N15" s="58"/>
+      <c r="O15" s="58"/>
+      <c r="Q15" s="47"/>
+      <c r="R15" s="47"/>
+      <c r="S15" s="47"/>
+      <c r="T15" s="47"/>
     </row>
     <row r="16" spans="1:22" ht="14.45" customHeight="1">
-      <c r="A16" s="59"/>
-      <c r="B16" s="59"/>
-      <c r="D16" s="59"/>
-      <c r="E16" s="59"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="49"/>
-      <c r="J16" s="49"/>
-      <c r="L16" s="50"/>
-      <c r="M16" s="50"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="50"/>
-      <c r="Q16" s="39"/>
-      <c r="R16" s="39"/>
-      <c r="S16" s="39"/>
-      <c r="T16" s="39"/>
+      <c r="A16" s="67"/>
+      <c r="B16" s="67"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="L16" s="58"/>
+      <c r="M16" s="58"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="58"/>
+      <c r="Q16" s="47"/>
+      <c r="R16" s="47"/>
+      <c r="S16" s="47"/>
+      <c r="T16" s="47"/>
     </row>
     <row r="17" spans="1:20" ht="14.45" customHeight="1">
-      <c r="A17" s="59"/>
-      <c r="B17" s="59"/>
-      <c r="D17" s="59"/>
-      <c r="E17" s="59"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="49"/>
-      <c r="J17" s="49"/>
-      <c r="L17" s="50"/>
-      <c r="M17" s="50"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="50"/>
-      <c r="Q17" s="39"/>
-      <c r="R17" s="39"/>
-      <c r="S17" s="39"/>
-      <c r="T17" s="39"/>
+      <c r="A17" s="67"/>
+      <c r="B17" s="67"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="57"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="58"/>
+      <c r="O17" s="58"/>
+      <c r="Q17" s="47"/>
+      <c r="R17" s="47"/>
+      <c r="S17" s="47"/>
+      <c r="T17" s="47"/>
     </row>
     <row r="18" spans="1:20" ht="14.45" customHeight="1">
-      <c r="A18" s="59"/>
-      <c r="B18" s="59"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="59"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
-      <c r="L18" s="50"/>
-      <c r="M18" s="50"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="50"/>
-      <c r="Q18" s="39"/>
-      <c r="R18" s="39"/>
-      <c r="S18" s="39"/>
-      <c r="T18" s="39"/>
+      <c r="A18" s="67"/>
+      <c r="B18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="57"/>
+      <c r="L18" s="58"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="58"/>
+      <c r="O18" s="58"/>
+      <c r="Q18" s="47"/>
+      <c r="R18" s="47"/>
+      <c r="S18" s="47"/>
+      <c r="T18" s="47"/>
     </row>
     <row r="19" spans="1:20" ht="14.45" customHeight="1">
-      <c r="A19" s="59"/>
-      <c r="B19" s="59"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="L19" s="50"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="50"/>
-      <c r="Q19" s="39"/>
-      <c r="R19" s="39"/>
-      <c r="S19" s="39"/>
-      <c r="T19" s="39"/>
+      <c r="A19" s="67"/>
+      <c r="B19" s="67"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="L19" s="58"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="58"/>
+      <c r="Q19" s="47"/>
+      <c r="R19" s="47"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="47"/>
     </row>
     <row r="20" spans="1:20" ht="14.45" customHeight="1">
-      <c r="A20" s="59"/>
-      <c r="B20" s="59"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="49"/>
-      <c r="L20" s="50"/>
-      <c r="M20" s="50"/>
-      <c r="N20" s="50"/>
-      <c r="O20" s="50"/>
-      <c r="Q20" s="39"/>
-      <c r="R20" s="39"/>
-      <c r="S20" s="39"/>
-      <c r="T20" s="39"/>
+      <c r="A20" s="67"/>
+      <c r="B20" s="67"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="57"/>
+      <c r="L20" s="58"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="58"/>
+      <c r="O20" s="58"/>
+      <c r="Q20" s="47"/>
+      <c r="R20" s="47"/>
+      <c r="S20" s="47"/>
+      <c r="T20" s="47"/>
     </row>
     <row r="21" spans="1:20" ht="14.45" customHeight="1">
-      <c r="A21" s="59"/>
-      <c r="B21" s="59"/>
-      <c r="D21" s="59"/>
-      <c r="E21" s="59"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="49"/>
-      <c r="L21" s="50"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="50"/>
-      <c r="Q21" s="39"/>
-      <c r="R21" s="39"/>
-      <c r="S21" s="39"/>
-      <c r="T21" s="39"/>
+      <c r="A21" s="67"/>
+      <c r="B21" s="67"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="57"/>
+      <c r="L21" s="58"/>
+      <c r="M21" s="58"/>
+      <c r="N21" s="58"/>
+      <c r="O21" s="58"/>
+      <c r="Q21" s="47"/>
+      <c r="R21" s="47"/>
+      <c r="S21" s="47"/>
+      <c r="T21" s="47"/>
     </row>
     <row r="22" spans="1:20" ht="14.45" customHeight="1">
-      <c r="A22" s="59"/>
-      <c r="B22" s="59"/>
-      <c r="D22" s="59"/>
-      <c r="E22" s="59"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="49"/>
-      <c r="L22" s="50"/>
-      <c r="M22" s="50"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="50"/>
-      <c r="Q22" s="39"/>
-      <c r="R22" s="39"/>
-      <c r="S22" s="39"/>
-      <c r="T22" s="39"/>
+      <c r="A22" s="67"/>
+      <c r="B22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="L22" s="58"/>
+      <c r="M22" s="58"/>
+      <c r="N22" s="58"/>
+      <c r="O22" s="58"/>
+      <c r="Q22" s="47"/>
+      <c r="R22" s="47"/>
+      <c r="S22" s="47"/>
+      <c r="T22" s="47"/>
     </row>
     <row r="23" spans="1:20" ht="14.45" customHeight="1">
-      <c r="A23" s="59"/>
-      <c r="B23" s="59"/>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
-      <c r="L23" s="50"/>
-      <c r="M23" s="50"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="50"/>
-      <c r="Q23" s="39"/>
-      <c r="R23" s="39"/>
-      <c r="S23" s="39"/>
-      <c r="T23" s="39"/>
+      <c r="A23" s="67"/>
+      <c r="B23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="L23" s="58"/>
+      <c r="M23" s="58"/>
+      <c r="N23" s="58"/>
+      <c r="O23" s="58"/>
+      <c r="Q23" s="47"/>
+      <c r="R23" s="47"/>
+      <c r="S23" s="47"/>
+      <c r="T23" s="47"/>
     </row>
     <row r="24" spans="1:20" ht="14.45" customHeight="1">
-      <c r="A24" s="59"/>
-      <c r="B24" s="59"/>
-      <c r="D24" s="59"/>
-      <c r="E24" s="59"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="49"/>
-      <c r="I24" s="49"/>
-      <c r="J24" s="49"/>
-      <c r="L24" s="50"/>
-      <c r="M24" s="50"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="50"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="39"/>
-      <c r="S24" s="39"/>
-      <c r="T24" s="39"/>
+      <c r="A24" s="67"/>
+      <c r="B24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="57"/>
+      <c r="J24" s="57"/>
+      <c r="L24" s="58"/>
+      <c r="M24" s="58"/>
+      <c r="N24" s="58"/>
+      <c r="O24" s="58"/>
+      <c r="Q24" s="47"/>
+      <c r="R24" s="47"/>
+      <c r="S24" s="47"/>
+      <c r="T24" s="47"/>
     </row>
     <row r="25" spans="1:20" ht="14.45" customHeight="1">
-      <c r="A25" s="59"/>
-      <c r="B25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="49"/>
-      <c r="I25" s="49"/>
-      <c r="J25" s="49"/>
-      <c r="L25" s="50"/>
-      <c r="M25" s="50"/>
-      <c r="N25" s="50"/>
-      <c r="O25" s="50"/>
-      <c r="Q25" s="39"/>
-      <c r="R25" s="39"/>
-      <c r="S25" s="39"/>
-      <c r="T25" s="39"/>
-    </row>
-    <row r="26" spans="1:20">
-      <c r="A26" s="59"/>
-      <c r="B26" s="59"/>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="L26" s="50"/>
-      <c r="M26" s="50"/>
-      <c r="N26" s="50"/>
-      <c r="O26" s="50"/>
-      <c r="Q26" s="39"/>
-      <c r="R26" s="39"/>
-      <c r="S26" s="39"/>
-      <c r="T26" s="39"/>
-    </row>
-    <row r="27" spans="1:20">
-      <c r="A27" s="59"/>
-      <c r="B27" s="59"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="49"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="L27" s="50"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="50"/>
-      <c r="Q27" s="39"/>
-      <c r="R27" s="39"/>
-      <c r="S27" s="39"/>
-      <c r="T27" s="39"/>
-    </row>
-    <row r="28" spans="1:20">
-      <c r="A28" s="59"/>
-      <c r="B28" s="59"/>
-      <c r="D28" s="59"/>
-      <c r="E28" s="59"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
-      <c r="L28" s="50"/>
-      <c r="M28" s="50"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="50"/>
-      <c r="Q28" s="39"/>
-      <c r="R28" s="39"/>
-      <c r="S28" s="39"/>
-      <c r="T28" s="39"/>
+      <c r="A25" s="67"/>
+      <c r="B25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="L25" s="58"/>
+      <c r="M25" s="58"/>
+      <c r="N25" s="58"/>
+      <c r="O25" s="58"/>
+      <c r="Q25" s="47"/>
+      <c r="R25" s="47"/>
+      <c r="S25" s="47"/>
+      <c r="T25" s="47"/>
+    </row>
+    <row r="26" spans="1:20" ht="15">
+      <c r="A26" s="67"/>
+      <c r="B26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="L26" s="58"/>
+      <c r="M26" s="58"/>
+      <c r="N26" s="58"/>
+      <c r="O26" s="58"/>
+      <c r="Q26" s="47"/>
+      <c r="R26" s="47"/>
+      <c r="S26" s="47"/>
+      <c r="T26" s="47"/>
+    </row>
+    <row r="27" spans="1:20" ht="15">
+      <c r="A27" s="67"/>
+      <c r="B27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="57"/>
+      <c r="L27" s="58"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="58"/>
+      <c r="O27" s="58"/>
+      <c r="Q27" s="47"/>
+      <c r="R27" s="47"/>
+      <c r="S27" s="47"/>
+      <c r="T27" s="47"/>
+    </row>
+    <row r="28" spans="1:20" ht="15">
+      <c r="A28" s="67"/>
+      <c r="B28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="67"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="57"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="58"/>
+      <c r="O28" s="58"/>
+      <c r="Q28" s="47"/>
+      <c r="R28" s="47"/>
+      <c r="S28" s="47"/>
+      <c r="T28" s="47"/>
     </row>
     <row r="29" spans="1:20" ht="19.5">
-      <c r="A29" s="59"/>
-      <c r="B29" s="59"/>
-      <c r="D29" s="59"/>
-      <c r="E29" s="59"/>
-      <c r="G29" s="49"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
-      <c r="L29" s="50"/>
-      <c r="M29" s="50"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="50"/>
+      <c r="A29" s="67"/>
+      <c r="B29" s="67"/>
+      <c r="D29" s="67"/>
+      <c r="E29" s="67"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="L29" s="58"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="58"/>
+      <c r="O29" s="58"/>
       <c r="Q29" s="34"/>
       <c r="R29" s="34"/>
       <c r="S29" s="34"/>
       <c r="T29" s="34"/>
     </row>
     <row r="30" spans="1:20" ht="14.45" customHeight="1">
-      <c r="A30" s="59"/>
-      <c r="B30" s="59"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="59"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="49"/>
-      <c r="L30" s="50"/>
-      <c r="M30" s="50"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="50"/>
-      <c r="Q30" s="52" t="s">
+      <c r="A30" s="67"/>
+      <c r="B30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="L30" s="58"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="58"/>
+      <c r="O30" s="58"/>
+      <c r="Q30" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="R30" s="60"/>
+      <c r="S30" s="60"/>
+      <c r="T30" s="61"/>
+    </row>
+    <row r="31" spans="1:20" ht="18.75">
+      <c r="A31" s="67"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="R30" s="52"/>
-      <c r="S30" s="52"/>
-      <c r="T30" s="53"/>
-    </row>
-    <row r="31" spans="1:20" ht="18.600000000000001">
-      <c r="A31" s="59"/>
-      <c r="B31" s="59"/>
-      <c r="C31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="59"/>
-      <c r="E31" s="59"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="49"/>
-      <c r="I31" s="49"/>
-      <c r="J31" s="49"/>
-      <c r="L31" s="50"/>
-      <c r="M31" s="50"/>
-      <c r="N31" s="50"/>
-      <c r="O31" s="50"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
+      <c r="J31" s="57"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="58"/>
       <c r="P31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q31" s="54"/>
-      <c r="R31" s="54"/>
-      <c r="S31" s="54"/>
-      <c r="T31" s="55"/>
+        <v>11</v>
+      </c>
+      <c r="Q31" s="62"/>
+      <c r="R31" s="62"/>
+      <c r="S31" s="62"/>
+      <c r="T31" s="63"/>
     </row>
     <row r="32" spans="1:20" ht="19.5">
-      <c r="A32" s="59"/>
-      <c r="B32" s="59"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="59"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="L32" s="50"/>
-      <c r="M32" s="50"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="50"/>
+      <c r="A32" s="67"/>
+      <c r="B32" s="67"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="67"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="57"/>
+      <c r="J32" s="57"/>
+      <c r="L32" s="58"/>
+      <c r="M32" s="58"/>
+      <c r="N32" s="58"/>
+      <c r="O32" s="58"/>
       <c r="Q32" s="34"/>
       <c r="R32" s="34"/>
       <c r="S32" s="34"/>
       <c r="T32" s="34"/>
     </row>
     <row r="33" spans="1:20" ht="14.45" customHeight="1">
-      <c r="A33" s="59"/>
-      <c r="B33" s="59"/>
-      <c r="D33" s="59"/>
-      <c r="E33" s="59"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="49"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="49"/>
-      <c r="L33" s="50"/>
-      <c r="M33" s="50"/>
-      <c r="N33" s="50"/>
-      <c r="O33" s="50"/>
-      <c r="Q33" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="R33" s="43"/>
-      <c r="S33" s="43"/>
-      <c r="T33" s="44"/>
+      <c r="A33" s="67"/>
+      <c r="B33" s="67"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="67"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="57"/>
+      <c r="L33" s="58"/>
+      <c r="M33" s="58"/>
+      <c r="N33" s="58"/>
+      <c r="O33" s="58"/>
+      <c r="Q33" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="R33" s="51"/>
+      <c r="S33" s="51"/>
+      <c r="T33" s="52"/>
     </row>
     <row r="34" spans="1:20" ht="14.45" customHeight="1">
-      <c r="A34" s="59"/>
-      <c r="B34" s="59"/>
-      <c r="D34" s="59"/>
-      <c r="E34" s="59"/>
-      <c r="G34" s="49"/>
-      <c r="H34" s="49"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="49"/>
-      <c r="L34" s="50"/>
-      <c r="M34" s="50"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="50"/>
+      <c r="A34" s="67"/>
+      <c r="B34" s="67"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="67"/>
+      <c r="G34" s="57"/>
+      <c r="H34" s="57"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
+      <c r="L34" s="58"/>
+      <c r="M34" s="58"/>
+      <c r="N34" s="58"/>
+      <c r="O34" s="58"/>
       <c r="P34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q34" s="45"/>
-      <c r="R34" s="45"/>
-      <c r="S34" s="45"/>
-      <c r="T34" s="46"/>
+        <v>11</v>
+      </c>
+      <c r="Q34" s="53"/>
+      <c r="R34" s="53"/>
+      <c r="S34" s="53"/>
+      <c r="T34" s="54"/>
     </row>
     <row r="35" spans="1:20" ht="19.5">
-      <c r="A35" s="59"/>
-      <c r="B35" s="59"/>
-      <c r="D35" s="59"/>
-      <c r="E35" s="59"/>
-      <c r="G35" s="49"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="49"/>
-      <c r="L35" s="50"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="50"/>
-      <c r="O35" s="50"/>
+      <c r="A35" s="67"/>
+      <c r="B35" s="67"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="57"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="57"/>
+      <c r="L35" s="58"/>
+      <c r="M35" s="58"/>
+      <c r="N35" s="58"/>
+      <c r="O35" s="58"/>
       <c r="Q35" s="34"/>
       <c r="R35" s="34"/>
       <c r="S35" s="34"/>
       <c r="T35" s="34"/>
     </row>
-    <row r="36" spans="1:20" ht="14.45" customHeight="1">
-      <c r="A36" s="59"/>
-      <c r="B36" s="59"/>
-      <c r="D36" s="59"/>
-      <c r="E36" s="59"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="49"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="49"/>
+    <row r="36" spans="1:20" ht="15">
+      <c r="A36" s="67"/>
+      <c r="B36" s="67"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="L36" s="58"/>
+      <c r="M36" s="58"/>
+      <c r="N36" s="58"/>
+      <c r="O36" s="58"/>
+      <c r="Q36" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="R36" s="51"/>
+      <c r="S36" s="51"/>
+      <c r="T36" s="52"/>
     </row>
     <row r="37" spans="1:20" ht="14.45" customHeight="1">
-      <c r="A37" s="59"/>
-      <c r="B37" s="59"/>
-      <c r="D37" s="59"/>
-      <c r="E37" s="59"/>
-      <c r="G37" s="49"/>
-      <c r="H37" s="49"/>
-      <c r="I37" s="49"/>
-      <c r="J37" s="49"/>
-    </row>
-    <row r="38" spans="1:20" ht="19.5">
-      <c r="A38" s="59"/>
-      <c r="B38" s="59"/>
-      <c r="D38" s="59"/>
-      <c r="E38" s="59"/>
-      <c r="G38" s="49"/>
-      <c r="H38" s="49"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="49"/>
-      <c r="L38" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="M38" s="50"/>
-      <c r="N38" s="50"/>
-      <c r="O38" s="50"/>
-      <c r="P38" s="34"/>
-      <c r="Q38" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="R38" s="37"/>
-      <c r="S38" s="37"/>
-      <c r="T38" s="38"/>
-    </row>
-    <row r="39" spans="1:20" ht="19.5" customHeight="1">
-      <c r="A39" s="59"/>
-      <c r="B39" s="59"/>
-      <c r="D39" s="59"/>
-      <c r="E39" s="59"/>
-      <c r="G39" s="49"/>
-      <c r="H39" s="49"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="49"/>
-      <c r="L39" s="50"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="50"/>
-      <c r="O39" s="50"/>
+      <c r="A37" s="67"/>
+      <c r="B37" s="67"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="L37" s="58"/>
+      <c r="M37" s="58"/>
+      <c r="N37" s="58"/>
+      <c r="O37" s="58"/>
+      <c r="P37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q37" s="53"/>
+      <c r="R37" s="53"/>
+      <c r="S37" s="53"/>
+      <c r="T37" s="54"/>
+    </row>
+    <row r="38" spans="1:20" ht="14.45" customHeight="1">
+      <c r="A38" s="67"/>
+      <c r="B38" s="67"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+    </row>
+    <row r="39" spans="1:20" ht="19.5">
+      <c r="A39" s="67"/>
+      <c r="B39" s="67"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="L39" s="58" t="s">
+        <v>15</v>
+      </c>
+      <c r="M39" s="58"/>
+      <c r="N39" s="58"/>
+      <c r="O39" s="58"/>
       <c r="P39" s="34"/>
-      <c r="Q39" s="39"/>
-      <c r="R39" s="39"/>
-      <c r="S39" s="39"/>
-      <c r="T39" s="40"/>
+      <c r="Q39" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="R39" s="45"/>
+      <c r="S39" s="45"/>
+      <c r="T39" s="46"/>
     </row>
     <row r="40" spans="1:20" ht="19.5" customHeight="1">
-      <c r="A40" s="59"/>
-      <c r="B40" s="59"/>
-      <c r="D40" s="59"/>
-      <c r="E40" s="59"/>
-      <c r="G40" s="49"/>
-      <c r="H40" s="49"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="49"/>
-      <c r="L40" s="50"/>
-      <c r="M40" s="50"/>
-      <c r="N40" s="50"/>
-      <c r="O40" s="50"/>
+      <c r="A40" s="67"/>
+      <c r="B40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="L40" s="58"/>
+      <c r="M40" s="58"/>
+      <c r="N40" s="58"/>
+      <c r="O40" s="58"/>
       <c r="P40" s="34"/>
-      <c r="Q40" s="39"/>
-      <c r="R40" s="39"/>
-      <c r="S40" s="39"/>
-      <c r="T40" s="40"/>
+      <c r="Q40" s="47"/>
+      <c r="R40" s="47"/>
+      <c r="S40" s="47"/>
+      <c r="T40" s="48"/>
     </row>
     <row r="41" spans="1:20" ht="19.5" customHeight="1">
-      <c r="A41" s="59"/>
-      <c r="B41" s="59"/>
-      <c r="D41" s="59"/>
-      <c r="E41" s="59"/>
-      <c r="G41" s="49"/>
-      <c r="H41" s="49"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="49"/>
-      <c r="L41" s="50"/>
-      <c r="M41" s="50"/>
-      <c r="N41" s="50"/>
-      <c r="O41" s="50"/>
+      <c r="A41" s="67"/>
+      <c r="B41" s="67"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="57"/>
+      <c r="L41" s="58"/>
+      <c r="M41" s="58"/>
+      <c r="N41" s="58"/>
+      <c r="O41" s="58"/>
       <c r="P41" s="34"/>
-      <c r="Q41" s="39"/>
-      <c r="R41" s="39"/>
-      <c r="S41" s="39"/>
-      <c r="T41" s="40"/>
+      <c r="Q41" s="47"/>
+      <c r="R41" s="47"/>
+      <c r="S41" s="47"/>
+      <c r="T41" s="48"/>
     </row>
     <row r="42" spans="1:20" ht="19.5" customHeight="1">
-      <c r="A42" s="59"/>
-      <c r="B42" s="59"/>
-      <c r="D42" s="59"/>
-      <c r="E42" s="59"/>
-      <c r="G42" s="49"/>
-      <c r="H42" s="49"/>
-      <c r="I42" s="49"/>
-      <c r="J42" s="49"/>
-      <c r="L42" s="50"/>
-      <c r="M42" s="50"/>
-      <c r="N42" s="50"/>
-      <c r="O42" s="50"/>
+      <c r="A42" s="67"/>
+      <c r="B42" s="67"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57"/>
+      <c r="L42" s="58"/>
+      <c r="M42" s="58"/>
+      <c r="N42" s="58"/>
+      <c r="O42" s="58"/>
       <c r="P42" s="34"/>
-      <c r="Q42" s="39"/>
-      <c r="R42" s="39"/>
-      <c r="S42" s="39"/>
-      <c r="T42" s="40"/>
-    </row>
-    <row r="43" spans="1:20" ht="14.45" customHeight="1">
-      <c r="A43" s="59"/>
-      <c r="B43" s="59"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="49"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="49"/>
-      <c r="L43" s="50"/>
-      <c r="M43" s="50"/>
-      <c r="N43" s="50"/>
-      <c r="O43" s="50"/>
-      <c r="P43" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q43" s="39"/>
-      <c r="R43" s="39"/>
-      <c r="S43" s="39"/>
-      <c r="T43" s="40"/>
-    </row>
-    <row r="44" spans="1:20" ht="19.5" customHeight="1">
-      <c r="A44" s="59"/>
-      <c r="B44" s="59"/>
-      <c r="D44" s="59"/>
-      <c r="E44" s="59"/>
-      <c r="G44" s="49"/>
-      <c r="H44" s="49"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="49"/>
-      <c r="L44" s="50"/>
-      <c r="M44" s="50"/>
-      <c r="N44" s="50"/>
-      <c r="O44" s="50"/>
-      <c r="P44" s="34"/>
-      <c r="Q44" s="39"/>
-      <c r="R44" s="39"/>
-      <c r="S44" s="39"/>
-      <c r="T44" s="40"/>
+      <c r="Q42" s="47"/>
+      <c r="R42" s="47"/>
+      <c r="S42" s="47"/>
+      <c r="T42" s="48"/>
+    </row>
+    <row r="43" spans="1:20" ht="19.5" customHeight="1">
+      <c r="A43" s="67"/>
+      <c r="B43" s="67"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="57"/>
+      <c r="L43" s="58"/>
+      <c r="M43" s="58"/>
+      <c r="N43" s="58"/>
+      <c r="O43" s="58"/>
+      <c r="P43" s="34"/>
+      <c r="Q43" s="47"/>
+      <c r="R43" s="47"/>
+      <c r="S43" s="47"/>
+      <c r="T43" s="48"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.45" customHeight="1">
+      <c r="A44" s="67"/>
+      <c r="B44" s="67"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="67"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="57"/>
+      <c r="L44" s="58"/>
+      <c r="M44" s="58"/>
+      <c r="N44" s="58"/>
+      <c r="O44" s="58"/>
+      <c r="P44" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q44" s="47"/>
+      <c r="R44" s="47"/>
+      <c r="S44" s="47"/>
+      <c r="T44" s="48"/>
     </row>
     <row r="45" spans="1:20" ht="19.5" customHeight="1">
-      <c r="A45" s="59"/>
-      <c r="B45" s="59"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59"/>
-      <c r="G45" s="49"/>
-      <c r="H45" s="49"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="49"/>
-      <c r="L45" s="50"/>
-      <c r="M45" s="50"/>
-      <c r="N45" s="50"/>
-      <c r="O45" s="50"/>
+      <c r="A45" s="67"/>
+      <c r="B45" s="67"/>
+      <c r="D45" s="67"/>
+      <c r="E45" s="67"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="57"/>
+      <c r="L45" s="58"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="58"/>
+      <c r="O45" s="58"/>
       <c r="P45" s="34"/>
-      <c r="Q45" s="39"/>
-      <c r="R45" s="39"/>
-      <c r="S45" s="39"/>
-      <c r="T45" s="40"/>
+      <c r="Q45" s="47"/>
+      <c r="R45" s="47"/>
+      <c r="S45" s="47"/>
+      <c r="T45" s="48"/>
     </row>
     <row r="46" spans="1:20" ht="19.5" customHeight="1">
-      <c r="A46" s="59"/>
-      <c r="B46" s="59"/>
-      <c r="D46" s="59"/>
-      <c r="E46" s="59"/>
-      <c r="G46" s="49"/>
-      <c r="H46" s="49"/>
-      <c r="I46" s="49"/>
-      <c r="J46" s="49"/>
-      <c r="L46" s="50"/>
-      <c r="M46" s="50"/>
-      <c r="N46" s="50"/>
-      <c r="O46" s="50"/>
+      <c r="A46" s="67"/>
+      <c r="B46" s="67"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="57"/>
+      <c r="J46" s="57"/>
+      <c r="L46" s="58"/>
+      <c r="M46" s="58"/>
+      <c r="N46" s="58"/>
+      <c r="O46" s="58"/>
       <c r="P46" s="34"/>
-      <c r="Q46" s="39"/>
-      <c r="R46" s="39"/>
-      <c r="S46" s="39"/>
-      <c r="T46" s="40"/>
+      <c r="Q46" s="47"/>
+      <c r="R46" s="47"/>
+      <c r="S46" s="47"/>
+      <c r="T46" s="48"/>
     </row>
     <row r="47" spans="1:20" ht="19.5" customHeight="1">
-      <c r="A47" s="59"/>
-      <c r="B47" s="59"/>
-      <c r="D47" s="59"/>
-      <c r="E47" s="59"/>
-      <c r="G47" s="49"/>
-      <c r="H47" s="49"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="49"/>
-      <c r="L47" s="50"/>
-      <c r="M47" s="50"/>
-      <c r="N47" s="50"/>
-      <c r="O47" s="50"/>
+      <c r="A47" s="67"/>
+      <c r="B47" s="67"/>
+      <c r="D47" s="67"/>
+      <c r="E47" s="67"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="57"/>
+      <c r="J47" s="57"/>
+      <c r="L47" s="58"/>
+      <c r="M47" s="58"/>
+      <c r="N47" s="58"/>
+      <c r="O47" s="58"/>
       <c r="P47" s="34"/>
-      <c r="Q47" s="39"/>
-      <c r="R47" s="39"/>
-      <c r="S47" s="39"/>
-      <c r="T47" s="40"/>
+      <c r="Q47" s="47"/>
+      <c r="R47" s="47"/>
+      <c r="S47" s="47"/>
+      <c r="T47" s="48"/>
     </row>
     <row r="48" spans="1:20" ht="19.5" customHeight="1">
-      <c r="A48" s="59"/>
-      <c r="B48" s="59"/>
-      <c r="D48" s="59"/>
-      <c r="E48" s="59"/>
-      <c r="G48" s="49"/>
-      <c r="H48" s="49"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="49"/>
-      <c r="K48" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="L48" s="50"/>
-      <c r="M48" s="50"/>
-      <c r="N48" s="50"/>
-      <c r="O48" s="50"/>
+      <c r="A48" s="67"/>
+      <c r="B48" s="67"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="67"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="57"/>
+      <c r="J48" s="57"/>
+      <c r="L48" s="58"/>
+      <c r="M48" s="58"/>
+      <c r="N48" s="58"/>
+      <c r="O48" s="58"/>
       <c r="P48" s="34"/>
-      <c r="Q48" s="39"/>
-      <c r="R48" s="39"/>
-      <c r="S48" s="39"/>
-      <c r="T48" s="40"/>
-    </row>
-    <row r="49" spans="1:20" ht="15.6" customHeight="1">
-      <c r="A49" s="59"/>
-      <c r="B49" s="59"/>
-      <c r="D49" s="59"/>
-      <c r="E49" s="59"/>
-      <c r="G49" s="49"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="49"/>
-      <c r="J49" s="49"/>
-      <c r="L49" s="50"/>
-      <c r="M49" s="50"/>
-      <c r="N49" s="50"/>
-      <c r="O49" s="50"/>
+      <c r="Q48" s="47"/>
+      <c r="R48" s="47"/>
+      <c r="S48" s="47"/>
+      <c r="T48" s="48"/>
+    </row>
+    <row r="49" spans="1:20" ht="19.5" customHeight="1">
+      <c r="A49" s="67"/>
+      <c r="B49" s="67"/>
+      <c r="D49" s="67"/>
+      <c r="E49" s="67"/>
+      <c r="G49" s="57"/>
+      <c r="H49" s="57"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="57"/>
+      <c r="K49" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="L49" s="58"/>
+      <c r="M49" s="58"/>
+      <c r="N49" s="58"/>
+      <c r="O49" s="58"/>
       <c r="P49" s="34"/>
-      <c r="Q49" s="41"/>
-      <c r="R49" s="41"/>
-      <c r="S49" s="41"/>
-      <c r="T49" s="42"/>
-    </row>
-    <row r="50" spans="1:20" ht="19.5" customHeight="1">
-      <c r="A50" s="59"/>
-      <c r="B50" s="59"/>
-      <c r="D50" s="59"/>
-      <c r="E50" s="59"/>
-      <c r="G50" s="49"/>
-      <c r="H50" s="49"/>
-      <c r="I50" s="49"/>
-      <c r="J50" s="49"/>
-      <c r="L50" s="50"/>
-      <c r="M50" s="50"/>
-      <c r="N50" s="50"/>
-      <c r="O50" s="50"/>
-      <c r="P50" s="86"/>
-      <c r="Q50" s="86"/>
-      <c r="R50" s="86"/>
+      <c r="Q49" s="47"/>
+      <c r="R49" s="47"/>
+      <c r="S49" s="47"/>
+      <c r="T49" s="48"/>
+    </row>
+    <row r="50" spans="1:20" ht="15.6" customHeight="1">
+      <c r="A50" s="67"/>
+      <c r="B50" s="67"/>
+      <c r="D50" s="67"/>
+      <c r="E50" s="67"/>
+      <c r="G50" s="57"/>
+      <c r="H50" s="57"/>
+      <c r="I50" s="57"/>
+      <c r="J50" s="57"/>
+      <c r="L50" s="58"/>
+      <c r="M50" s="58"/>
+      <c r="N50" s="58"/>
+      <c r="O50" s="58"/>
+      <c r="P50" s="34"/>
+      <c r="Q50" s="49"/>
+      <c r="R50" s="49"/>
+      <c r="S50" s="49"/>
+      <c r="T50" s="50"/>
     </row>
     <row r="51" spans="1:20" ht="19.5" customHeight="1">
-      <c r="A51" s="59"/>
-      <c r="B51" s="59"/>
-      <c r="D51" s="59"/>
-      <c r="E51" s="59"/>
-      <c r="G51" s="49"/>
-      <c r="H51" s="49"/>
-      <c r="I51" s="49"/>
-      <c r="J51" s="49"/>
-      <c r="L51" s="51"/>
-      <c r="M51" s="51"/>
-      <c r="N51" s="51"/>
-      <c r="O51" s="51"/>
-      <c r="P51" s="86"/>
-      <c r="Q51" s="86"/>
-      <c r="R51" s="86"/>
+      <c r="A51" s="67"/>
+      <c r="B51" s="67"/>
+      <c r="D51" s="67"/>
+      <c r="E51" s="67"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="57"/>
+      <c r="J51" s="57"/>
+      <c r="L51" s="58"/>
+      <c r="M51" s="58"/>
+      <c r="N51" s="58"/>
+      <c r="O51" s="58"/>
+      <c r="P51" s="95"/>
+      <c r="Q51" s="95"/>
+      <c r="R51" s="95"/>
     </row>
     <row r="52" spans="1:20" ht="19.5" customHeight="1">
-      <c r="A52" s="59"/>
-      <c r="B52" s="59"/>
-      <c r="D52" s="59"/>
-      <c r="E52" s="59"/>
-      <c r="G52" s="49"/>
-      <c r="H52" s="49"/>
-      <c r="I52" s="49"/>
-      <c r="J52" s="49"/>
-      <c r="P52" s="86"/>
-      <c r="Q52" s="86"/>
-      <c r="R52" s="86"/>
+      <c r="A52" s="67"/>
+      <c r="B52" s="67"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
+      <c r="G52" s="57"/>
+      <c r="H52" s="57"/>
+      <c r="I52" s="57"/>
+      <c r="J52" s="57"/>
+      <c r="L52" s="59"/>
+      <c r="M52" s="59"/>
+      <c r="N52" s="59"/>
+      <c r="O52" s="59"/>
+      <c r="P52" s="95"/>
+      <c r="Q52" s="95"/>
+      <c r="R52" s="95"/>
     </row>
     <row r="53" spans="1:20" ht="19.5" customHeight="1">
-      <c r="A53" s="59"/>
-      <c r="B53" s="59"/>
-      <c r="D53" s="59"/>
-      <c r="E53" s="59"/>
-      <c r="G53" s="49"/>
-      <c r="H53" s="49"/>
-      <c r="I53" s="49"/>
-      <c r="J53" s="49"/>
-      <c r="L53" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="M53" s="62"/>
-      <c r="N53" s="62"/>
-      <c r="O53" s="63"/>
-      <c r="P53" s="86"/>
-      <c r="Q53" s="86"/>
-      <c r="R53" s="86"/>
+      <c r="A53" s="67"/>
+      <c r="B53" s="67"/>
+      <c r="D53" s="67"/>
+      <c r="E53" s="67"/>
+      <c r="G53" s="57"/>
+      <c r="H53" s="57"/>
+      <c r="I53" s="57"/>
+      <c r="J53" s="57"/>
+      <c r="P53" s="95"/>
+      <c r="Q53" s="95"/>
+      <c r="R53" s="95"/>
     </row>
     <row r="54" spans="1:20" ht="19.5" customHeight="1">
-      <c r="A54" s="59"/>
-      <c r="B54" s="59"/>
-      <c r="D54" s="59"/>
-      <c r="E54" s="59"/>
-      <c r="G54" s="49"/>
-      <c r="H54" s="49"/>
-      <c r="I54" s="49"/>
-      <c r="J54" s="49"/>
-      <c r="K54" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L54" s="64"/>
-      <c r="M54" s="65"/>
-      <c r="N54" s="65"/>
-      <c r="O54" s="66"/>
-      <c r="P54" s="86"/>
-      <c r="Q54" s="86"/>
-      <c r="R54" s="86"/>
+      <c r="A54" s="67"/>
+      <c r="B54" s="67"/>
+      <c r="D54" s="67"/>
+      <c r="E54" s="67"/>
+      <c r="G54" s="57"/>
+      <c r="H54" s="57"/>
+      <c r="I54" s="57"/>
+      <c r="J54" s="57"/>
+      <c r="L54" s="69" t="s">
+        <v>17</v>
+      </c>
+      <c r="M54" s="70"/>
+      <c r="N54" s="70"/>
+      <c r="O54" s="71"/>
+      <c r="P54" s="95"/>
+      <c r="Q54" s="95"/>
+      <c r="R54" s="95"/>
     </row>
     <row r="55" spans="1:20" ht="19.5" customHeight="1">
-      <c r="A55" s="59"/>
-      <c r="B55" s="59"/>
-      <c r="D55" s="59"/>
-      <c r="E55" s="59"/>
-      <c r="G55" s="49"/>
-      <c r="H55" s="49"/>
-      <c r="I55" s="49"/>
-      <c r="J55" s="49"/>
-      <c r="L55" s="64"/>
-      <c r="M55" s="65"/>
-      <c r="N55" s="65"/>
-      <c r="O55" s="66"/>
-    </row>
-    <row r="56" spans="1:20">
-      <c r="A56" s="59"/>
-      <c r="B56" s="59"/>
-      <c r="D56" s="59"/>
-      <c r="E56" s="59"/>
-      <c r="G56" s="49"/>
-      <c r="H56" s="49"/>
-      <c r="I56" s="49"/>
-      <c r="J56" s="49"/>
-      <c r="L56" s="67"/>
-      <c r="M56" s="68"/>
-      <c r="N56" s="68"/>
-      <c r="O56" s="69"/>
+      <c r="A55" s="67"/>
+      <c r="B55" s="67"/>
+      <c r="D55" s="67"/>
+      <c r="E55" s="67"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="57"/>
+      <c r="J55" s="57"/>
+      <c r="K55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L55" s="72"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="73"/>
+      <c r="O55" s="74"/>
+      <c r="P55" s="95"/>
+      <c r="Q55" s="95"/>
+      <c r="R55" s="95"/>
+    </row>
+    <row r="56" spans="1:20" ht="19.5" customHeight="1">
+      <c r="A56" s="67"/>
+      <c r="B56" s="67"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="67"/>
+      <c r="G56" s="57"/>
+      <c r="H56" s="57"/>
+      <c r="I56" s="57"/>
+      <c r="J56" s="57"/>
+      <c r="L56" s="72"/>
+      <c r="M56" s="73"/>
+      <c r="N56" s="73"/>
+      <c r="O56" s="74"/>
     </row>
     <row r="57" spans="1:20">
-      <c r="A57" s="59"/>
-      <c r="B57" s="59"/>
-      <c r="D57" s="59"/>
-      <c r="E57" s="59"/>
-      <c r="G57" s="49"/>
-      <c r="H57" s="49"/>
-      <c r="I57" s="49"/>
-      <c r="J57" s="49"/>
+      <c r="A57" s="67"/>
+      <c r="B57" s="67"/>
+      <c r="D57" s="67"/>
+      <c r="E57" s="67"/>
+      <c r="G57" s="57"/>
+      <c r="H57" s="57"/>
+      <c r="I57" s="57"/>
+      <c r="J57" s="57"/>
+      <c r="L57" s="75"/>
+      <c r="M57" s="76"/>
+      <c r="N57" s="76"/>
+      <c r="O57" s="77"/>
     </row>
     <row r="58" spans="1:20">
-      <c r="A58" s="59"/>
-      <c r="B58" s="59"/>
-      <c r="D58" s="59"/>
-      <c r="E58" s="59"/>
-      <c r="G58" s="49"/>
-      <c r="H58" s="49"/>
-      <c r="I58" s="49"/>
-      <c r="J58" s="49"/>
-      <c r="L58" s="70" t="s">
-        <v>16</v>
-      </c>
-      <c r="M58" s="87"/>
-      <c r="N58" s="87"/>
-      <c r="O58" s="88"/>
-    </row>
-    <row r="59" spans="1:20" ht="18.600000000000001">
-      <c r="A59" s="59"/>
-      <c r="B59" s="59"/>
-      <c r="D59" s="59"/>
-      <c r="E59" s="59"/>
-      <c r="G59" s="49"/>
-      <c r="H59" s="49"/>
-      <c r="I59" s="49"/>
-      <c r="J59" s="49"/>
-      <c r="K59" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L59" s="89"/>
-      <c r="M59" s="86"/>
-      <c r="N59" s="86"/>
-      <c r="O59" s="90"/>
-    </row>
-    <row r="60" spans="1:20">
-      <c r="A60" s="59"/>
-      <c r="B60" s="59"/>
-      <c r="D60" s="59"/>
-      <c r="E60" s="59"/>
-      <c r="G60" s="49"/>
-      <c r="H60" s="49"/>
-      <c r="I60" s="49"/>
-      <c r="J60" s="49"/>
-      <c r="L60" s="89"/>
-      <c r="M60" s="86"/>
-      <c r="N60" s="86"/>
-      <c r="O60" s="90"/>
+      <c r="A58" s="67"/>
+      <c r="B58" s="67"/>
+      <c r="D58" s="67"/>
+      <c r="E58" s="67"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="57"/>
+      <c r="I58" s="57"/>
+      <c r="J58" s="57"/>
+    </row>
+    <row r="59" spans="1:20">
+      <c r="A59" s="67"/>
+      <c r="B59" s="67"/>
+      <c r="D59" s="67"/>
+      <c r="E59" s="67"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="57"/>
+      <c r="I59" s="57"/>
+      <c r="J59" s="57"/>
+      <c r="L59" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="M59" s="96"/>
+      <c r="N59" s="96"/>
+      <c r="O59" s="97"/>
+    </row>
+    <row r="60" spans="1:20" ht="18.600000000000001">
+      <c r="A60" s="67"/>
+      <c r="B60" s="67"/>
+      <c r="D60" s="67"/>
+      <c r="E60" s="67"/>
+      <c r="G60" s="57"/>
+      <c r="H60" s="57"/>
+      <c r="I60" s="57"/>
+      <c r="J60" s="57"/>
+      <c r="K60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L60" s="98"/>
+      <c r="M60" s="95"/>
+      <c r="N60" s="95"/>
+      <c r="O60" s="99"/>
     </row>
     <row r="61" spans="1:20">
-      <c r="A61" s="59"/>
-      <c r="B61" s="59"/>
-      <c r="D61" s="59"/>
-      <c r="E61" s="59"/>
-      <c r="G61" s="49"/>
-      <c r="H61" s="49"/>
-      <c r="I61" s="49"/>
-      <c r="J61" s="49"/>
-      <c r="L61" s="91"/>
-      <c r="M61" s="92"/>
-      <c r="N61" s="92"/>
-      <c r="O61" s="93"/>
+      <c r="A61" s="67"/>
+      <c r="B61" s="67"/>
+      <c r="D61" s="67"/>
+      <c r="E61" s="67"/>
+      <c r="G61" s="57"/>
+      <c r="H61" s="57"/>
+      <c r="I61" s="57"/>
+      <c r="J61" s="57"/>
+      <c r="L61" s="98"/>
+      <c r="M61" s="95"/>
+      <c r="N61" s="95"/>
+      <c r="O61" s="99"/>
     </row>
     <row r="62" spans="1:20">
-      <c r="A62" s="59"/>
-      <c r="B62" s="59"/>
-      <c r="D62" s="59"/>
-      <c r="E62" s="59"/>
+      <c r="A62" s="67"/>
+      <c r="B62" s="67"/>
+      <c r="D62" s="67"/>
+      <c r="E62" s="67"/>
+      <c r="G62" s="57"/>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
+      <c r="J62" s="57"/>
+      <c r="L62" s="100"/>
+      <c r="M62" s="101"/>
+      <c r="N62" s="101"/>
+      <c r="O62" s="102"/>
     </row>
     <row r="63" spans="1:20">
-      <c r="A63" s="59"/>
-      <c r="B63" s="59"/>
-      <c r="D63" s="59"/>
-      <c r="E63" s="59"/>
-      <c r="G63" s="60" t="s">
-        <v>17</v>
-      </c>
-      <c r="H63" s="87"/>
-      <c r="I63" s="87"/>
-      <c r="J63" s="88"/>
+      <c r="A63" s="67"/>
+      <c r="B63" s="67"/>
+      <c r="D63" s="67"/>
+      <c r="E63" s="67"/>
     </row>
     <row r="64" spans="1:20">
-      <c r="A64" s="59"/>
-      <c r="B64" s="59"/>
-      <c r="D64" s="59"/>
-      <c r="E64" s="59"/>
-      <c r="G64" s="89"/>
-      <c r="H64" s="86"/>
-      <c r="I64" s="86"/>
-      <c r="J64" s="90"/>
-    </row>
-    <row r="65" spans="1:15" ht="18.600000000000001">
-      <c r="A65" s="59"/>
-      <c r="B65" s="59"/>
-      <c r="D65" s="59"/>
-      <c r="E65" s="59"/>
-      <c r="F65" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G65" s="89"/>
-      <c r="H65" s="86"/>
-      <c r="I65" s="86"/>
-      <c r="J65" s="90"/>
-    </row>
-    <row r="66" spans="1:15">
-      <c r="A66" s="59"/>
-      <c r="B66" s="59"/>
-      <c r="D66" s="59"/>
-      <c r="E66" s="59"/>
-      <c r="G66" s="89"/>
-      <c r="H66" s="86"/>
-      <c r="I66" s="86"/>
-      <c r="J66" s="90"/>
+      <c r="A64" s="67"/>
+      <c r="B64" s="67"/>
+      <c r="D64" s="67"/>
+      <c r="E64" s="67"/>
+      <c r="G64" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" s="96"/>
+      <c r="I64" s="96"/>
+      <c r="J64" s="97"/>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" s="67"/>
+      <c r="B65" s="67"/>
+      <c r="D65" s="67"/>
+      <c r="E65" s="67"/>
+      <c r="G65" s="98"/>
+      <c r="H65" s="95"/>
+      <c r="I65" s="95"/>
+      <c r="J65" s="99"/>
+    </row>
+    <row r="66" spans="1:15" ht="18.600000000000001">
+      <c r="A66" s="67"/>
+      <c r="B66" s="67"/>
+      <c r="D66" s="67"/>
+      <c r="E66" s="67"/>
+      <c r="F66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G66" s="98"/>
+      <c r="H66" s="95"/>
+      <c r="I66" s="95"/>
+      <c r="J66" s="99"/>
     </row>
     <row r="67" spans="1:15">
-      <c r="A67" s="59"/>
-      <c r="B67" s="59"/>
-      <c r="D67" s="59"/>
-      <c r="E67" s="59"/>
-      <c r="G67" s="91"/>
-      <c r="H67" s="92"/>
-      <c r="I67" s="92"/>
-      <c r="J67" s="93"/>
+      <c r="A67" s="67"/>
+      <c r="B67" s="67"/>
+      <c r="D67" s="67"/>
+      <c r="E67" s="67"/>
+      <c r="G67" s="98"/>
+      <c r="H67" s="95"/>
+      <c r="I67" s="95"/>
+      <c r="J67" s="99"/>
     </row>
     <row r="68" spans="1:15">
-      <c r="A68" s="59"/>
-      <c r="B68" s="59"/>
-      <c r="D68" s="59"/>
-      <c r="E68" s="59"/>
+      <c r="A68" s="67"/>
+      <c r="B68" s="67"/>
+      <c r="D68" s="67"/>
+      <c r="E68" s="67"/>
+      <c r="G68" s="100"/>
+      <c r="H68" s="101"/>
+      <c r="I68" s="101"/>
+      <c r="J68" s="102"/>
     </row>
     <row r="69" spans="1:15">
-      <c r="A69" s="59"/>
-      <c r="B69" s="59"/>
-      <c r="D69" s="59"/>
-      <c r="E69" s="59"/>
+      <c r="A69" s="67"/>
+      <c r="B69" s="67"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="67"/>
     </row>
     <row r="70" spans="1:15">
-      <c r="A70" s="59"/>
-      <c r="B70" s="59"/>
-      <c r="D70" s="59"/>
-      <c r="E70" s="59"/>
-    </row>
-    <row r="71" spans="1:15" ht="14.45" customHeight="1">
-      <c r="A71" s="59"/>
-      <c r="B71" s="59"/>
-      <c r="D71" s="59"/>
-      <c r="E71" s="59"/>
-      <c r="G71" s="57" t="s">
-        <v>18</v>
-      </c>
-      <c r="H71" s="57"/>
-      <c r="I71" s="57"/>
-      <c r="J71" s="57"/>
-      <c r="L71" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="M71" s="37"/>
-      <c r="N71" s="37"/>
-      <c r="O71" s="38"/>
-    </row>
-    <row r="72" spans="1:15">
-      <c r="A72" s="59"/>
-      <c r="B72" s="59"/>
-      <c r="D72" s="59"/>
-      <c r="E72" s="59"/>
-      <c r="G72" s="57"/>
-      <c r="H72" s="57"/>
-      <c r="I72" s="57"/>
-      <c r="J72" s="57"/>
-      <c r="L72" s="39"/>
-      <c r="M72" s="39"/>
-      <c r="N72" s="39"/>
-      <c r="O72" s="40"/>
+      <c r="A70" s="67"/>
+      <c r="B70" s="67"/>
+      <c r="D70" s="67"/>
+      <c r="E70" s="67"/>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71" s="67"/>
+      <c r="B71" s="67"/>
+      <c r="D71" s="67"/>
+      <c r="E71" s="67"/>
+    </row>
+    <row r="72" spans="1:15" ht="14.45" customHeight="1">
+      <c r="A72" s="67"/>
+      <c r="B72" s="67"/>
+      <c r="D72" s="67"/>
+      <c r="E72" s="67"/>
+      <c r="G72" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" s="65"/>
+      <c r="I72" s="65"/>
+      <c r="J72" s="65"/>
+      <c r="L72" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="M72" s="45"/>
+      <c r="N72" s="45"/>
+      <c r="O72" s="46"/>
     </row>
     <row r="73" spans="1:15">
-      <c r="A73" s="59"/>
-      <c r="B73" s="59"/>
-      <c r="D73" s="59"/>
-      <c r="E73" s="59"/>
-      <c r="G73" s="57"/>
-      <c r="H73" s="57"/>
-      <c r="I73" s="57"/>
-      <c r="J73" s="57"/>
-      <c r="L73" s="39"/>
-      <c r="M73" s="39"/>
-      <c r="N73" s="39"/>
-      <c r="O73" s="40"/>
+      <c r="A73" s="67"/>
+      <c r="B73" s="67"/>
+      <c r="D73" s="67"/>
+      <c r="E73" s="67"/>
+      <c r="G73" s="65"/>
+      <c r="H73" s="65"/>
+      <c r="I73" s="65"/>
+      <c r="J73" s="65"/>
+      <c r="L73" s="47"/>
+      <c r="M73" s="47"/>
+      <c r="N73" s="47"/>
+      <c r="O73" s="48"/>
     </row>
     <row r="74" spans="1:15">
-      <c r="A74" s="59"/>
-      <c r="B74" s="59"/>
-      <c r="D74" s="59"/>
-      <c r="E74" s="59"/>
-      <c r="G74" s="57"/>
-      <c r="H74" s="57"/>
-      <c r="I74" s="57"/>
-      <c r="J74" s="57"/>
-      <c r="L74" s="39"/>
-      <c r="M74" s="39"/>
-      <c r="N74" s="39"/>
-      <c r="O74" s="40"/>
+      <c r="A74" s="67"/>
+      <c r="B74" s="67"/>
+      <c r="D74" s="67"/>
+      <c r="E74" s="67"/>
+      <c r="G74" s="65"/>
+      <c r="H74" s="65"/>
+      <c r="I74" s="65"/>
+      <c r="J74" s="65"/>
+      <c r="L74" s="47"/>
+      <c r="M74" s="47"/>
+      <c r="N74" s="47"/>
+      <c r="O74" s="48"/>
     </row>
     <row r="75" spans="1:15">
-      <c r="A75" s="59"/>
-      <c r="B75" s="59"/>
-      <c r="D75" s="59"/>
-      <c r="E75" s="59"/>
-      <c r="G75" s="57"/>
-      <c r="H75" s="57"/>
-      <c r="I75" s="57"/>
-      <c r="J75" s="57"/>
-      <c r="L75" s="39"/>
-      <c r="M75" s="39"/>
-      <c r="N75" s="39"/>
-      <c r="O75" s="40"/>
+      <c r="A75" s="67"/>
+      <c r="B75" s="67"/>
+      <c r="D75" s="67"/>
+      <c r="E75" s="67"/>
+      <c r="G75" s="65"/>
+      <c r="H75" s="65"/>
+      <c r="I75" s="65"/>
+      <c r="J75" s="65"/>
+      <c r="L75" s="47"/>
+      <c r="M75" s="47"/>
+      <c r="N75" s="47"/>
+      <c r="O75" s="48"/>
     </row>
     <row r="76" spans="1:15">
-      <c r="A76" s="59"/>
-      <c r="B76" s="59"/>
-      <c r="D76" s="59"/>
-      <c r="E76" s="59"/>
-      <c r="G76" s="57"/>
-      <c r="H76" s="57"/>
-      <c r="I76" s="57"/>
-      <c r="J76" s="57"/>
-      <c r="L76" s="39"/>
-      <c r="M76" s="39"/>
-      <c r="N76" s="39"/>
-      <c r="O76" s="40"/>
+      <c r="A76" s="67"/>
+      <c r="B76" s="67"/>
+      <c r="D76" s="67"/>
+      <c r="E76" s="67"/>
+      <c r="G76" s="65"/>
+      <c r="H76" s="65"/>
+      <c r="I76" s="65"/>
+      <c r="J76" s="65"/>
+      <c r="L76" s="47"/>
+      <c r="M76" s="47"/>
+      <c r="N76" s="47"/>
+      <c r="O76" s="48"/>
     </row>
     <row r="77" spans="1:15">
-      <c r="A77" s="59"/>
-      <c r="B77" s="59"/>
-      <c r="D77" s="59"/>
-      <c r="E77" s="59"/>
-      <c r="G77" s="57"/>
-      <c r="H77" s="57"/>
-      <c r="I77" s="57"/>
-      <c r="J77" s="57"/>
-      <c r="L77" s="39"/>
-      <c r="M77" s="39"/>
-      <c r="N77" s="39"/>
-      <c r="O77" s="40"/>
+      <c r="A77" s="67"/>
+      <c r="B77" s="67"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="67"/>
+      <c r="G77" s="65"/>
+      <c r="H77" s="65"/>
+      <c r="I77" s="65"/>
+      <c r="J77" s="65"/>
+      <c r="L77" s="47"/>
+      <c r="M77" s="47"/>
+      <c r="N77" s="47"/>
+      <c r="O77" s="48"/>
     </row>
     <row r="78" spans="1:15">
-      <c r="A78" s="59"/>
-      <c r="B78" s="59"/>
-      <c r="D78" s="59"/>
-      <c r="E78" s="59"/>
-      <c r="G78" s="57"/>
-      <c r="H78" s="57"/>
-      <c r="I78" s="57"/>
-      <c r="J78" s="57"/>
-      <c r="L78" s="39"/>
-      <c r="M78" s="39"/>
-      <c r="N78" s="39"/>
-      <c r="O78" s="40"/>
-    </row>
-    <row r="79" spans="1:15" ht="18.600000000000001">
-      <c r="A79" s="59"/>
-      <c r="B79" s="59"/>
-      <c r="D79" s="59"/>
-      <c r="E79" s="59"/>
-      <c r="F79" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G79" s="57"/>
-      <c r="H79" s="57"/>
-      <c r="I79" s="57"/>
-      <c r="J79" s="57"/>
-      <c r="K79" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L79" s="39"/>
-      <c r="M79" s="39"/>
-      <c r="N79" s="39"/>
-      <c r="O79" s="40"/>
-    </row>
-    <row r="80" spans="1:15">
-      <c r="A80" s="59"/>
-      <c r="B80" s="59"/>
-      <c r="D80" s="59"/>
-      <c r="E80" s="59"/>
-      <c r="G80" s="57"/>
-      <c r="H80" s="57"/>
-      <c r="I80" s="57"/>
-      <c r="J80" s="57"/>
-      <c r="L80" s="39"/>
-      <c r="M80" s="39"/>
-      <c r="N80" s="39"/>
-      <c r="O80" s="40"/>
+      <c r="A78" s="67"/>
+      <c r="B78" s="67"/>
+      <c r="D78" s="67"/>
+      <c r="E78" s="67"/>
+      <c r="G78" s="65"/>
+      <c r="H78" s="65"/>
+      <c r="I78" s="65"/>
+      <c r="J78" s="65"/>
+      <c r="L78" s="47"/>
+      <c r="M78" s="47"/>
+      <c r="N78" s="47"/>
+      <c r="O78" s="48"/>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" s="67"/>
+      <c r="B79" s="67"/>
+      <c r="D79" s="67"/>
+      <c r="E79" s="67"/>
+      <c r="G79" s="65"/>
+      <c r="H79" s="65"/>
+      <c r="I79" s="65"/>
+      <c r="J79" s="65"/>
+      <c r="L79" s="47"/>
+      <c r="M79" s="47"/>
+      <c r="N79" s="47"/>
+      <c r="O79" s="48"/>
+    </row>
+    <row r="80" spans="1:15" ht="18.600000000000001">
+      <c r="A80" s="67"/>
+      <c r="B80" s="67"/>
+      <c r="D80" s="67"/>
+      <c r="E80" s="67"/>
+      <c r="F80" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G80" s="65"/>
+      <c r="H80" s="65"/>
+      <c r="I80" s="65"/>
+      <c r="J80" s="65"/>
+      <c r="K80" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L80" s="47"/>
+      <c r="M80" s="47"/>
+      <c r="N80" s="47"/>
+      <c r="O80" s="48"/>
     </row>
     <row r="81" spans="1:15">
-      <c r="A81" s="59"/>
-      <c r="B81" s="59"/>
-      <c r="D81" s="59"/>
-      <c r="E81" s="59"/>
-      <c r="G81" s="57"/>
-      <c r="H81" s="57"/>
-      <c r="I81" s="57"/>
-      <c r="J81" s="57"/>
-      <c r="L81" s="39"/>
-      <c r="M81" s="39"/>
-      <c r="N81" s="39"/>
-      <c r="O81" s="40"/>
+      <c r="A81" s="67"/>
+      <c r="B81" s="67"/>
+      <c r="D81" s="67"/>
+      <c r="E81" s="67"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="J81" s="65"/>
+      <c r="L81" s="47"/>
+      <c r="M81" s="47"/>
+      <c r="N81" s="47"/>
+      <c r="O81" s="48"/>
     </row>
     <row r="82" spans="1:15">
-      <c r="A82" s="59"/>
-      <c r="B82" s="59"/>
-      <c r="D82" s="59"/>
-      <c r="E82" s="59"/>
-      <c r="G82" s="57"/>
-      <c r="H82" s="57"/>
-      <c r="I82" s="57"/>
-      <c r="J82" s="57"/>
-      <c r="L82" s="41"/>
-      <c r="M82" s="41"/>
-      <c r="N82" s="41"/>
-      <c r="O82" s="42"/>
-    </row>
-    <row r="85" spans="1:15" ht="15.6">
-      <c r="A85" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="86" spans="1:15">
-      <c r="A86" s="4"/>
-      <c r="B86" s="5" t="s">
-        <v>21</v>
+      <c r="A82" s="67"/>
+      <c r="B82" s="67"/>
+      <c r="D82" s="67"/>
+      <c r="E82" s="67"/>
+      <c r="G82" s="65"/>
+      <c r="H82" s="65"/>
+      <c r="I82" s="65"/>
+      <c r="J82" s="65"/>
+      <c r="L82" s="47"/>
+      <c r="M82" s="47"/>
+      <c r="N82" s="47"/>
+      <c r="O82" s="48"/>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83" s="67"/>
+      <c r="B83" s="67"/>
+      <c r="D83" s="67"/>
+      <c r="E83" s="67"/>
+      <c r="G83" s="65"/>
+      <c r="H83" s="65"/>
+      <c r="I83" s="65"/>
+      <c r="J83" s="65"/>
+      <c r="L83" s="49"/>
+      <c r="M83" s="49"/>
+      <c r="N83" s="49"/>
+      <c r="O83" s="50"/>
+    </row>
+    <row r="86" spans="1:15" ht="15.6">
+      <c r="A86" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:15">
-      <c r="A87" s="6"/>
+      <c r="A87" s="4"/>
       <c r="B87" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:15">
-      <c r="A88" s="7"/>
+      <c r="A88" s="6"/>
       <c r="B88" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:15">
-      <c r="A89" s="8"/>
+      <c r="A89" s="7"/>
       <c r="B89" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:15">
-      <c r="A90" s="9"/>
+      <c r="A90" s="8"/>
       <c r="B90" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
+      <c r="A91" s="9"/>
+      <c r="B91" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="L71:O82"/>
-    <mergeCell ref="G71:J82"/>
-    <mergeCell ref="D5:E82"/>
-    <mergeCell ref="A5:B82"/>
-    <mergeCell ref="G63:J67"/>
-    <mergeCell ref="L53:O56"/>
-    <mergeCell ref="L58:O61"/>
-    <mergeCell ref="Q38:T49"/>
+  <mergeCells count="22">
+    <mergeCell ref="L72:O83"/>
+    <mergeCell ref="G72:J83"/>
+    <mergeCell ref="D5:E83"/>
+    <mergeCell ref="A5:B83"/>
+    <mergeCell ref="G64:J68"/>
+    <mergeCell ref="L54:O57"/>
+    <mergeCell ref="L59:O62"/>
+    <mergeCell ref="L5:O37"/>
+    <mergeCell ref="Q39:T50"/>
     <mergeCell ref="Q33:T34"/>
     <mergeCell ref="A1:V1"/>
-    <mergeCell ref="G5:J61"/>
-    <mergeCell ref="L38:O51"/>
+    <mergeCell ref="G5:J62"/>
+    <mergeCell ref="L39:O52"/>
     <mergeCell ref="Q30:T31"/>
     <mergeCell ref="Q5:T28"/>
-    <mergeCell ref="L5:O35"/>
-    <mergeCell ref="P50:R54"/>
+    <mergeCell ref="P51:R55"/>
+    <mergeCell ref="Q36:T37"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="Q3:T3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3120,45 +4044,92 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
     <col min="3" max="3" width="120" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1">
+    <row r="1" spans="1:5" ht="15" thickBot="1">
       <c r="A1" s="31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="32" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C1" s="32" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="409.5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15">
       <c r="A3" s="10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>32</v>
+        <v>7</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="409.6">
+      <c r="A4" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="37"/>
+    </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15">
+      <c r="A6" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="41"/>
+      <c r="E6" s="40"/>
+    </row>
+    <row r="7" spans="1:5" ht="15">
+      <c r="A7" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -3180,31 +4151,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="75" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
+      <c r="A1" s="84" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="12" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="18.95" customHeight="1">
@@ -3212,899 +4183,899 @@
         <v>1</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="14"/>
       <c r="D3" s="15" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F3" s="17"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="77">
+      <c r="A4" s="86">
         <v>2</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="18"/>
-      <c r="D4" s="78" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4" s="80" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="82" t="s">
-        <v>43</v>
+      <c r="D4" s="87" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="89" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="91" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="98.1" customHeight="1">
-      <c r="A5" s="77"/>
+      <c r="A5" s="86"/>
       <c r="B5" s="19" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C5" s="19"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="83"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="92"/>
     </row>
     <row r="6" spans="1:6" ht="44.45" customHeight="1">
       <c r="A6" s="16">
         <v>3</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="21" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A7" s="75" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="76"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="76"/>
+      <c r="A7" s="84" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
     </row>
     <row r="8" spans="1:6" ht="14.45" customHeight="1">
-      <c r="A8" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="84" t="s">
-        <v>48</v>
+      <c r="A8" s="82" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="93" t="s">
+        <v>57</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="71" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="73" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="73" t="s">
-        <v>51</v>
+        <v>58</v>
+      </c>
+      <c r="D8" s="80" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="82" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="82" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="74"/>
-      <c r="B9" s="85"/>
+      <c r="A9" s="83"/>
+      <c r="B9" s="94"/>
       <c r="C9" s="25"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B27" s="24" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15">
       <c r="A30" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15">
       <c r="A31" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D35" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D38" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D39" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D40" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D41" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="D42" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="20.100000000000001">
       <c r="A43" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D45" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D46" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D47" s="28" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D48" s="29" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D49" s="29" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
